--- a/demo_import/00_chart_of_accounts.xlsx
+++ b/demo_import/00_chart_of_accounts.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H310"/>
+  <dimension ref="A1:H329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -2184,9 +2184,9 @@
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Raw Coffee Stock</t>
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Robusta Stock</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>12010101</t>
+          <t>12010110</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -2205,7 +2205,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2218,22 +2218,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Screen 18 Stock</t>
+          <t>Robusta FAQ Stock</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Stock Account</t>
+          <t>Robusta Stock</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>12010102</t>
+          <t>12010111</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>12010100</t>
+          <t>12010110</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -2250,22 +2250,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Screen 15 Stock</t>
+          <t>Robusta Screen 18 Stock</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Stock Account</t>
+          <t>Robusta Stock</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>12010103</t>
+          <t>12010112</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>12010100</t>
+          <t>12010110</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -2282,22 +2282,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Screen 12 Stock</t>
+          <t>Robusta Screen 15 Stock</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Stock Account</t>
+          <t>Robusta Stock</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>12010104</t>
+          <t>12010113</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>12010100</t>
+          <t>12010110</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -2314,22 +2314,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Undergrades Stock</t>
+          <t>Robusta Screen 12 Stock</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Stock Account</t>
+          <t>Robusta Stock</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>12010105</t>
+          <t>12010114</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>12010100</t>
+          <t>12010110</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2346,22 +2346,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>By-products Stock</t>
+          <t>Robusta Undergrades Stock</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Stock Account</t>
+          <t>Robusta Stock</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>12010106</t>
+          <t>12010115</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>12010100</t>
+          <t>12010110</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2378,7 +2378,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Damages/Expiries</t>
+          <t>Arabica Stock</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2388,40 +2388,44 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>12010200</t>
+          <t>12010120</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>12010000</t>
+          <t>12010100</t>
         </is>
       </c>
       <c r="E65" t="n">
         <v>1</v>
       </c>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Inventory - Damages/Expired</t>
+          <t>Arabica Parchment Stock</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Damages/Expiries</t>
+          <t>Arabica Stock</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>12010501</t>
+          <t>12010121</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>12010200</t>
+          <t>12010120</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2436,60 +2440,64 @@
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Trade Receivables</t>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Arabica Screen 18 Stock</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Current Assets</t>
+          <t>Arabica Stock</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>12020000</t>
+          <t>12010122</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>12000000</t>
+          <t>12010120</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Customer Control Accounts</t>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Arabica Screen 15 Stock</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Trade Receivables</t>
+          <t>Arabica Stock</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>12020100</t>
+          <t>12010123</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>12020000</t>
+          <t>12010120</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Receivable</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -2498,22 +2506,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Export Customers</t>
+          <t>Arabica Screen 12 Stock</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Customer Control Accounts</t>
+          <t>Arabica Stock</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>12020101</t>
+          <t>12010124</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>12020100</t>
+          <t>12010120</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2521,7 +2529,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Receivable</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -2530,22 +2538,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Local Customers</t>
+          <t>Arabica Undergrades Stock</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Customer Control Accounts</t>
+          <t>Arabica Stock</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>12020102</t>
+          <t>12010125</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>12020100</t>
+          <t>12010120</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2553,211 +2561,215 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Receivable</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>Unallocated Recievables</t>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>By-products Stock</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Trade Receivables</t>
+          <t>Stock Account</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>12020110</t>
+          <t>12010130</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>12020000</t>
+          <t>12010100</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Unallocated Recievables</t>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Damages/Expiries</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Unallocated Recievables</t>
+          <t>Stock Account</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>12020105</t>
+          <t>12010200</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>12020110</t>
+          <t>12010000</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Receivable</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>Cash &amp; Bank Equivalents</t>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Inventory - Damages/Expired</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Current Assets</t>
+          <t>Damages/Expiries</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>12030000</t>
+          <t>12010501</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>12000000</t>
+          <t>12010200</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Bank Equivalents</t>
+          <t>Trade Receivables</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cash &amp; Bank Equivalents</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>12030100</t>
+          <t>12020000</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>12030000</t>
+          <t>12000000</t>
         </is>
       </c>
       <c r="E74" t="n">
         <v>1</v>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>ABSA Bank (UGX)</t>
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Customer Control Accounts</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bank Equivalents</t>
+          <t>Trade Receivables</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>12030107</t>
+          <t>12020100</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>12030100</t>
+          <t>12020000</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Receivable</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Cash Accounts</t>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Export Customers</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cash &amp; Bank Equivalents</t>
+          <t>Customer Control Accounts</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>12030300</t>
+          <t>12020101</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>12030000</t>
+          <t>12020100</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Receivable</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Airtel Money Pay</t>
+          <t>Local Customers</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cash Accounts</t>
+          <t>Customer Control Accounts</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>12030301</t>
+          <t>12020102</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>12030300</t>
+          <t>12020100</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2765,131 +2777,127 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Receivable</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Momo Pay</t>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Unallocated Recievables</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cash Accounts</t>
+          <t>Trade Receivables</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>12030303</t>
+          <t>12020110</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>12030300</t>
+          <t>12020000</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Post Dated Cheques</t>
+          <t>Unallocated Recievables</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cash Accounts</t>
+          <t>Unallocated Recievables</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>12030304</t>
+          <t>12020105</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>12030300</t>
+          <t>12020110</t>
         </is>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Receivable</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Cash - In -Hand</t>
+          <t>Cash &amp; Bank Equivalents</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cash &amp; Bank Equivalents</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>12030400</t>
+          <t>12030000</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>12030000</t>
+          <t>12000000</t>
         </is>
       </c>
       <c r="E80" t="n">
         <v>1</v>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Petty Cash</t>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Bank Equivalents</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cash - In -Hand</t>
+          <t>Cash &amp; Bank Equivalents</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>12030401</t>
+          <t>12030100</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>12030400</t>
+          <t>12030000</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -2898,54 +2906,58 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Donation-Clearing A/c</t>
+          <t>ABSA Bank (UGX)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cash - In -Hand</t>
+          <t>Bank Equivalents</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>12030402</t>
+          <t>12030107</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>12030400</t>
+          <t>12030100</t>
         </is>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
-      <c r="F82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Cash Lost A/C</t>
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Cash Accounts</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cash - In -Hand</t>
+          <t>Cash &amp; Bank Equivalents</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>12030403</t>
+          <t>12030300</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>12030400</t>
+          <t>12030000</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
@@ -2954,22 +2966,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CASH ACCOUNT</t>
+          <t>Airtel Money Pay</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cash - In -Hand</t>
+          <t>Cash Accounts</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>12030404</t>
+          <t>12030301</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>12030400</t>
+          <t>12030300</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2977,7 +2989,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -2986,54 +2998,58 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Bounced Cheque</t>
+          <t>Momo Pay</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cash - In -Hand</t>
+          <t>Cash Accounts</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>12030405</t>
+          <t>12030303</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>12030400</t>
+          <t>12030300</t>
         </is>
       </c>
       <c r="E85" t="n">
         <v>0</v>
       </c>
-      <c r="F85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Other Receivables</t>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Post Dated Cheques</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Current Assets</t>
+          <t>Cash Accounts</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>12040000</t>
+          <t>12030304</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>12000000</t>
+          <t>12030300</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
@@ -3042,82 +3058,90 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Related Party Receivables - Staff Advance</t>
+          <t>Cash - In -Hand</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Other Receivables</t>
+          <t>Cash &amp; Bank Equivalents</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>12040100</t>
+          <t>12030400</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>12040000</t>
+          <t>12030000</t>
         </is>
       </c>
       <c r="E87" t="n">
         <v>1</v>
       </c>
-      <c r="F87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Staff Advances</t>
+          <t>Petty Cash</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Related Party Receivables - Staff Advance</t>
+          <t>Cash - In -Hand</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>12040102</t>
+          <t>12030401</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>12040100</t>
+          <t>12030400</t>
         </is>
       </c>
       <c r="E88" t="n">
         <v>0</v>
       </c>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>Other Receivables</t>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Donation-Clearing A/c</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Other Receivables</t>
+          <t>Cash - In -Hand</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>12040200</t>
+          <t>12030402</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>12040000</t>
+          <t>12030400</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
@@ -3126,22 +3150,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Staff Loan</t>
+          <t>Cash Lost A/C</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Other Receivables</t>
+          <t>Cash - In -Hand</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>12040201</t>
+          <t>12030403</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>12040200</t>
+          <t>12030400</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -3154,50 +3178,54 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Directors Loan Receivable</t>
+          <t>CASH ACCOUNT</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Other Receivables</t>
+          <t>Cash - In -Hand</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>12040202</t>
+          <t>12030404</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>12040200</t>
+          <t>12030400</t>
         </is>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Tax Receivable</t>
+          <t>Bounced Cheque</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Other Receivables</t>
+          <t>Cash - In -Hand</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>12040203</t>
+          <t>12030405</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>12040200</t>
+          <t>12030400</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -3208,37 +3236,37 @@
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Other Receivables</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Other Receivables</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>12040204</t>
+          <t>12040000</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>12040200</t>
+          <t>12000000</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Withholding Tax Recivable</t>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Related Party Receivables - Staff Advance</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3248,16 +3276,16 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>12040205</t>
+          <t>12040100</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>12040200</t>
+          <t>12040000</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
@@ -3266,22 +3294,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Staff Advance</t>
+          <t>Staff Advances</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Other Receivables</t>
+          <t>Related Party Receivables - Staff Advance</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>12040206</t>
+          <t>12040102</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>12040200</t>
+          <t>12040100</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -3294,7 +3322,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Prepayments Expenses</t>
+          <t>Other Receivables</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3304,7 +3332,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>12040300</t>
+          <t>12040200</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -3322,22 +3350,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Prepaid Insurance</t>
+          <t>Staff Loan</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Prepayments Expenses</t>
+          <t>Other Receivables</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>12040301</t>
+          <t>12040201</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>12040300</t>
+          <t>12040200</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -3350,22 +3378,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Supplier Advance</t>
+          <t>Directors Loan Receivable</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Prepayments Expenses</t>
+          <t>Other Receivables</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>12040302</t>
+          <t>12040202</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>12040300</t>
+          <t>12040200</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -3378,22 +3406,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Prepaid Rent</t>
+          <t>Tax Receivable</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Prepayments Expenses</t>
+          <t>Other Receivables</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>12040303</t>
+          <t>12040203</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>12040300</t>
+          <t>12040200</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -3406,22 +3434,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Prepaid Tax</t>
+          <t>Other Receivables</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Prepayments Expenses</t>
+          <t>Other Receivables</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>12040304</t>
+          <t>12040204</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>12040300</t>
+          <t>12040200</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -3434,22 +3462,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Withholding Tax</t>
+          <t>Withholding Tax Recivable</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Prepayments Expenses</t>
+          <t>Other Receivables</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>12040306</t>
+          <t>12040205</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>12040300</t>
+          <t>12040200</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -3462,22 +3490,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Other Prepayments</t>
+          <t>Staff Advance</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Prepayments Expenses</t>
+          <t>Other Receivables</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>12040307</t>
+          <t>12040206</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>12040300</t>
+          <t>12040200</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -3490,7 +3518,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Prepayment To Suppliers</t>
+          <t>Prepayments Expenses</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3500,7 +3528,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>12040400</t>
+          <t>12040300</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -3518,22 +3546,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Prepayment - International Suppliers</t>
+          <t>Prepaid Insurance</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Prepayment To Suppliers</t>
+          <t>Prepayments Expenses</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>12040401</t>
+          <t>12040301</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>12040400</t>
+          <t>12040300</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -3546,22 +3574,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Prepayment - Local Suppliers</t>
+          <t>Supplier Advance</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Prepayment To Suppliers</t>
+          <t>Prepayments Expenses</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>12040402</t>
+          <t>12040302</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>12040400</t>
+          <t>12040300</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -3572,164 +3600,168 @@
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>Liabilities</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Prepaid Rent</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Prepayments Expenses</t>
+        </is>
+      </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>20000000</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr"/>
+          <t>12040303</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>12040300</t>
+        </is>
+      </c>
       <c r="E106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Liability</t>
-        </is>
-      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>Non Current Liabilities</t>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Prepaid Tax</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Liabilities</t>
+          <t>Prepayments Expenses</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>21000000</t>
+          <t>12040304</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>20000000</t>
+          <t>12040300</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>Long Term Liability</t>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Withholding Tax</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Non Current Liabilities</t>
+          <t>Prepayments Expenses</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>21010000</t>
+          <t>12040306</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>21000000</t>
+          <t>12040300</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>Mortgage Loan</t>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Other Prepayments</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Long Term Liability</t>
+          <t>Prepayments Expenses</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>21010100</t>
+          <t>12040307</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>21010000</t>
+          <t>12040300</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Mortgage Loan Payable</t>
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Prepayment To Suppliers</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Mortgage Loan</t>
+          <t>Other Receivables</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>21010101</t>
+          <t>12040400</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>21010100</t>
+          <t>12040000</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>Bank Loan</t>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Prepayment - International Suppliers</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Long Term Liability</t>
+          <t>Prepayment To Suppliers</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>21010200</t>
+          <t>12040401</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>21010000</t>
+          <t>12040400</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
@@ -3738,22 +3770,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Bank Loan Payable</t>
+          <t>Prepayment - Local Suppliers</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Bank Loan</t>
+          <t>Prepayment To Suppliers</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>21010201</t>
+          <t>12040402</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>21010200</t>
+          <t>12040400</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -3766,54 +3798,50 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Related Party Borrowings</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Long Term Liability</t>
-        </is>
-      </c>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>21010300</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>21010000</t>
-        </is>
-      </c>
+          <t>20000000</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr"/>
       <c r="E113" t="n">
         <v>1</v>
       </c>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Liability</t>
+        </is>
+      </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Directors Loan Payable</t>
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Non Current Liabilities</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Related Party Borrowings</t>
+          <t>Liabilities</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>21010301</t>
+          <t>21000000</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>21010300</t>
+          <t>20000000</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
@@ -3822,7 +3850,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Short Term Liability</t>
+          <t>Long Term Liability</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3832,7 +3860,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>21020000</t>
+          <t>21010000</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -3850,22 +3878,22 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Bank Loan Short Term Liabily</t>
+          <t>Mortgage Loan</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Short Term Liability</t>
+          <t>Long Term Liability</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>21020100</t>
+          <t>21010100</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>21020000</t>
+          <t>21010000</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -3878,22 +3906,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Short Term Loan Payable</t>
+          <t>Mortgage Loan Payable</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Bank Loan Short Term Liabily</t>
+          <t>Mortgage Loan</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>21020101</t>
+          <t>21010101</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>21020100</t>
+          <t>21010100</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -3906,22 +3934,22 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>Bank Loan</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Liabilities</t>
+          <t>Long Term Liability</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>22000000</t>
+          <t>21010200</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>20000000</t>
+          <t>21010000</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -3932,28 +3960,28 @@
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>Trade Payables</t>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Bank Loan Payable</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>Bank Loan</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>22010000</t>
+          <t>21010201</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>22000000</t>
+          <t>21010200</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
@@ -3962,22 +3990,22 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Accounts Payables</t>
+          <t>Related Party Borrowings</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Trade Payables</t>
+          <t>Long Term Liability</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>22010100</t>
+          <t>21010300</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>22010000</t>
+          <t>21010000</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -3990,94 +4018,82 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Creditors Control - Local</t>
+          <t>Directors Loan Payable</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Accounts Payables</t>
+          <t>Related Party Borrowings</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>22010101</t>
+          <t>21010301</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>22010100</t>
+          <t>21010300</t>
         </is>
       </c>
       <c r="E121" t="n">
         <v>0</v>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Payable</t>
-        </is>
-      </c>
+      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Creditors Control - Foreign (GBP)</t>
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Short Term Liability</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Accounts Payables</t>
+          <t>Non Current Liabilities</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>22010102</t>
+          <t>21020000</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>22010100</t>
+          <t>21000000</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Payable</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
+      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Reconciliation difference</t>
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Bank Loan Short Term Liabily</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Accounts Payables</t>
+          <t>Short Term Liability</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>22010103</t>
+          <t>21020100</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>22010100</t>
+          <t>21020000</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
@@ -4086,58 +4102,50 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Credit Control Account Foreign (USD)</t>
+          <t>Short Term Loan Payable</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Accounts Payables</t>
+          <t>Bank Loan Short Term Liabily</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>22010104</t>
+          <t>21020101</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>22010100</t>
+          <t>21020100</t>
         </is>
       </c>
       <c r="E124" t="n">
         <v>0</v>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Payable</t>
-        </is>
-      </c>
+      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Insurance Payable</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Trade Payables</t>
+          <t>Liabilities</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>22010200</t>
+          <t>22000000</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>22010000</t>
+          <t>20000000</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -4148,28 +4156,28 @@
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Insurance- Gds In Transit/po.n.-9000/062/1/00217/2017</t>
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Trade Payables</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Insurance Payable</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>22010201</t>
+          <t>22010000</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>22010200</t>
+          <t>22000000</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
@@ -4178,7 +4186,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Stock Liability</t>
+          <t>Accounts Payables</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4188,7 +4196,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>22010400</t>
+          <t>22010100</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
@@ -4206,22 +4214,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Goods Received But Not Invoiced</t>
+          <t>Creditors Control - Local</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Stock Liability</t>
+          <t>Accounts Payables</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>22010401</t>
+          <t>22010101</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>22010400</t>
+          <t>22010100</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -4229,63 +4237,71 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stock Received But Not Billed</t>
+          <t>Payable</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>Other Payables</t>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Creditors Control - Foreign (GBP)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>Accounts Payables</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>22020000</t>
+          <t>22010102</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>22000000</t>
+          <t>22010100</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1</v>
-      </c>
-      <c r="F129" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Payable</t>
+        </is>
+      </c>
       <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>Other Payables</t>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Reconciliation difference</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Other Payables</t>
+          <t>Accounts Payables</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>22020100</t>
+          <t>22010103</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>22020000</t>
+          <t>22010100</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
@@ -4294,54 +4310,62 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Interest Payable</t>
+          <t>Credit Control Account Foreign (USD)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Other Payables</t>
+          <t>Accounts Payables</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>22020101</t>
+          <t>22010104</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>22020100</t>
+          <t>22010100</t>
         </is>
       </c>
       <c r="E131" t="n">
         <v>0</v>
       </c>
-      <c r="F131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Payable</t>
+        </is>
+      </c>
       <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Other Payables</t>
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Payable</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Other Payables</t>
+          <t>Trade Payables</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>22020102</t>
+          <t>22010200</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>22020100</t>
+          <t>22010000</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
@@ -4350,22 +4374,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Savings Payable</t>
+          <t>Insurance- Gds In Transit/po.n.-9000/062/1/00217/2017</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Other Payables</t>
+          <t>Insurance Payable</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>22020103</t>
+          <t>22010201</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>22020100</t>
+          <t>22010200</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -4376,28 +4400,28 @@
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Security Deposit Payable</t>
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Stock Liability</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Other Payables</t>
+          <t>Trade Payables</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>22020104</t>
+          <t>22010400</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>22020100</t>
+          <t>22010000</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
@@ -4406,50 +4430,54 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Employee Control</t>
+          <t>Goods Received But Not Invoiced</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Other Payables</t>
+          <t>Stock Liability</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>22020205</t>
+          <t>22010401</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>22020100</t>
+          <t>22010400</t>
         </is>
       </c>
       <c r="E135" t="n">
         <v>0</v>
       </c>
-      <c r="F135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Stock Received But Not Billed</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Interest Payable</t>
+          <t>Other Payables</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Other Payables</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>22020200</t>
+          <t>22020000</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>22020000</t>
+          <t>22000000</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -4460,84 +4488,84 @@
       <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Interest Payable</t>
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Other Payables</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Interest Payable</t>
+          <t>Other Payables</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>22020201</t>
+          <t>22020100</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>22020200</t>
+          <t>22020000</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>Landed Costs</t>
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Interest Payable</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>Other Payables</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>22030000</t>
+          <t>22020101</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>22000000</t>
+          <t>22020100</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>landed Cost Accounts</t>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Other Payables</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Landed Costs</t>
+          <t>Other Payables</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>22030100</t>
+          <t>22020102</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>22030000</t>
+          <t>22020100</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
@@ -4546,22 +4574,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Agency Fee</t>
+          <t>Savings Payable</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>landed Cost Accounts</t>
+          <t>Other Payables</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>22030101</t>
+          <t>22020103</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>22030100</t>
+          <t>22020100</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -4574,22 +4602,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Excise Duty</t>
+          <t>Security Deposit Payable</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>landed Cost Accounts</t>
+          <t>Other Payables</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>22030103</t>
+          <t>22020104</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>22030100</t>
+          <t>22020100</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -4602,22 +4630,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Freight</t>
+          <t>Employee Control</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>landed Cost Accounts</t>
+          <t>Other Payables</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>22030104</t>
+          <t>22020205</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>22030100</t>
+          <t>22020100</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -4625,35 +4653,31 @@
       </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
+      <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>ICD Handling</t>
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Interest Payable</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>landed Cost Accounts</t>
+          <t>Other Payables</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>22030105</t>
+          <t>22020200</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>22030100</t>
+          <t>22020000</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
@@ -4662,22 +4686,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Import Duty</t>
+          <t>Interest Payable</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>landed Cost Accounts</t>
+          <t>Interest Payable</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>22030106</t>
+          <t>22020201</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>22030100</t>
+          <t>22020200</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -4688,56 +4712,56 @@
       <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Transport</t>
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Landed Costs</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>landed Cost Accounts</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>22030107</t>
+          <t>22030000</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>22030100</t>
+          <t>22000000</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Storage</t>
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>landed Cost Accounts</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>landed Cost Accounts</t>
+          <t>Landed Costs</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>22030110</t>
+          <t>22030100</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>22030100</t>
+          <t>22030000</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
@@ -4746,7 +4770,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Clearance Uganda</t>
+          <t>Agency Fee</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4756,7 +4780,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>22030112</t>
+          <t>22030101</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -4774,7 +4798,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Infrastructure Levy</t>
+          <t>Excise Duty</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4784,7 +4808,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>22030117</t>
+          <t>22030103</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
@@ -4802,7 +4826,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Freight GBP</t>
+          <t>Freight</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4812,7 +4836,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>22030124</t>
+          <t>22030104</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -4832,56 +4856,56 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>Tax Payables</t>
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>ICD Handling</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>landed Cost Accounts</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>22040000</t>
+          <t>22030105</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>22000000</t>
+          <t>22030100</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>Tax Liabilities</t>
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Import Duty</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Tax Payables</t>
+          <t>landed Cost Accounts</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>22040100</t>
+          <t>22030106</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>22040000</t>
+          <t>22030100</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr"/>
@@ -4890,22 +4914,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Corporation Tax Payable</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Tax Liabilities</t>
+          <t>landed Cost Accounts</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>22040102</t>
+          <t>22030107</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>22040100</t>
+          <t>22030100</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -4918,54 +4942,50 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Withholding Tax Payable</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Tax Liabilities</t>
+          <t>landed Cost Accounts</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>22040103</t>
+          <t>22030110</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>22040100</t>
+          <t>22030100</t>
         </is>
       </c>
       <c r="E153" t="n">
         <v>0</v>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Tax</t>
-        </is>
-      </c>
+      <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Local Service Tax Payable</t>
+          <t>Clearance Uganda</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Tax Liabilities</t>
+          <t>landed Cost Accounts</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>22040104</t>
+          <t>22030112</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>22040100</t>
+          <t>22030100</t>
         </is>
       </c>
       <c r="E154" t="n">
@@ -4978,22 +4998,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Deffered Tax Payable</t>
+          <t>Infrastructure Levy</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Tax Liabilities</t>
+          <t>landed Cost Accounts</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>22040105</t>
+          <t>22030117</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>22040100</t>
+          <t>22030100</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -5006,103 +5026,95 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Other Tax Payable</t>
+          <t>Freight GBP</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Tax Liabilities</t>
+          <t>landed Cost Accounts</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>22040106</t>
+          <t>22030124</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>22040100</t>
+          <t>22030100</t>
         </is>
       </c>
       <c r="E156" t="n">
         <v>0</v>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Tax</t>
-        </is>
-      </c>
+      <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Excise Duty Tax Payable</t>
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Tax Payables</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Tax Liabilities</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>22040107</t>
+          <t>22040000</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>22040100</t>
+          <t>22000000</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0</v>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Tax</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Vat Payable</t>
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Tax Liabilities</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Tax Liabilities</t>
+          <t>Tax Payables</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>22040101</t>
+          <t>22040100</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>22040100</t>
+          <t>22040000</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Tax</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Income Tax Payable</t>
+          <t>Corporation Tax Payable</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5112,7 +5124,7 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>22040108</t>
+          <t>22040102</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
@@ -5128,56 +5140,60 @@
       <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>Payroll Liabilities</t>
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Withholding Tax Payable</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>Tax Liabilities</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>22050000</t>
+          <t>22040103</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>22000000</t>
+          <t>22040100</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1</v>
-      </c>
-      <c r="F160" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>Payroll Liabilities</t>
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Local Service Tax Payable</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Payroll Liabilities</t>
+          <t>Tax Liabilities</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>22050100</t>
+          <t>22040104</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>22050000</t>
+          <t>22040100</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr"/>
@@ -5186,22 +5202,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Payroll Payable</t>
+          <t>Deffered Tax Payable</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Payroll Liabilities</t>
+          <t>Tax Liabilities</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>22050101</t>
+          <t>22040105</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>22050100</t>
+          <t>22040100</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -5214,106 +5230,118 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Paye Payable</t>
+          <t>Other Tax Payable</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Payroll Liabilities</t>
+          <t>Tax Liabilities</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>22050102</t>
+          <t>22040106</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>22050100</t>
+          <t>22040100</t>
         </is>
       </c>
       <c r="E163" t="n">
         <v>0</v>
       </c>
-      <c r="F163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Nssf Payable</t>
+          <t>Excise Duty Tax Payable</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Payroll Liabilities</t>
+          <t>Tax Liabilities</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>22050103</t>
+          <t>22040107</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>22050100</t>
+          <t>22040100</t>
         </is>
       </c>
       <c r="E164" t="n">
         <v>0</v>
       </c>
-      <c r="F164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Employee Saving Scheme</t>
+          <t>Vat Payable</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Payroll Liabilities</t>
+          <t>Tax Liabilities</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>22050104</t>
+          <t>22040101</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>22050100</t>
+          <t>22040100</t>
         </is>
       </c>
       <c r="E165" t="n">
         <v>0</v>
       </c>
-      <c r="F165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Employee Health Ins Payable</t>
+          <t>Income Tax Payable</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Payroll Liabilities</t>
+          <t>Tax Liabilities</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>22050105</t>
+          <t>22040108</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>22050100</t>
+          <t>22040100</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -5324,37 +5352,37 @@
       <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Worker's Compensation</t>
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Payroll Liabilities</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Payroll Liabilities</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>22050106</t>
+          <t>22050000</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>22050100</t>
+          <t>22000000</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Staff Other Expenses Payable</t>
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Payroll Liabilities</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5364,16 +5392,16 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>22050107</t>
+          <t>22050100</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>22050100</t>
+          <t>22050000</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
@@ -5382,7 +5410,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Staff Advances</t>
+          <t>Payroll Payable</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5392,7 +5420,7 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>22050108</t>
+          <t>22050101</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
@@ -5408,56 +5436,56 @@
       <c r="H169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>Provisions &amp; Accruals</t>
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Paye Payable</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>Payroll Liabilities</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>22060000</t>
+          <t>22050102</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>22000000</t>
+          <t>22050100</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>Provisions &amp; Accruals</t>
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Nssf Payable</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Provisions &amp; Accruals</t>
+          <t>Payroll Liabilities</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>22060100</t>
+          <t>22050103</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>22060000</t>
+          <t>22050100</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr"/>
@@ -5466,22 +5494,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Warranties</t>
+          <t>Employee Saving Scheme</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Provisions &amp; Accruals</t>
+          <t>Payroll Liabilities</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>22060101</t>
+          <t>22050104</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>22060100</t>
+          <t>22050100</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -5492,28 +5520,28 @@
       <c r="H172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>Deferred Income</t>
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Employee Health Ins Payable</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Provisions &amp; Accruals</t>
+          <t>Payroll Liabilities</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>22060200</t>
+          <t>22050105</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>22060000</t>
+          <t>22050100</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr"/>
@@ -5522,22 +5550,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Deferred Income (unearned Revenue)</t>
+          <t>Worker's Compensation</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Deferred Income</t>
+          <t>Payroll Liabilities</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>22060201</t>
+          <t>22050106</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>22060200</t>
+          <t>22050100</t>
         </is>
       </c>
       <c r="E174" t="n">
@@ -5548,52 +5576,56 @@
       <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>Equity &amp; Reserve</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr"/>
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Staff Other Expenses Payable</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Payroll Liabilities</t>
+        </is>
+      </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>30000000</t>
-        </is>
-      </c>
-      <c r="D175" s="3" t="inlineStr"/>
+          <t>22050107</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>22050100</t>
+        </is>
+      </c>
       <c r="E175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
+      <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>Equity &amp; Reserve</t>
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Staff Advances</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Equity &amp; Reserve</t>
+          <t>Payroll Liabilities</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>31000000</t>
+          <t>22050108</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>30000000</t>
+          <t>22050100</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
@@ -5602,22 +5634,22 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Capital &amp; Reserves</t>
+          <t>Provisions &amp; Accruals</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Equity &amp; Reserve</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>31010000</t>
+          <t>22060000</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>31000000</t>
+          <t>22000000</t>
         </is>
       </c>
       <c r="E177" t="n">
@@ -5630,22 +5662,22 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Share Capital</t>
+          <t>Provisions &amp; Accruals</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Capital &amp; Reserves</t>
+          <t>Provisions &amp; Accruals</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>31010100</t>
+          <t>22060100</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>31010000</t>
+          <t>22060000</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -5658,22 +5690,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Ordinary Share Capital</t>
+          <t>Warranties</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Share Capital</t>
+          <t>Provisions &amp; Accruals</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>31010101</t>
+          <t>22060101</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>31010100</t>
+          <t>22060100</t>
         </is>
       </c>
       <c r="E179" t="n">
@@ -5684,28 +5716,28 @@
       <c r="H179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Preferred Shares</t>
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Deferred Income</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Share Capital</t>
+          <t>Provisions &amp; Accruals</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>31010102</t>
+          <t>22060200</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>31010100</t>
+          <t>22060000</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr"/>
@@ -5714,22 +5746,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Share Premium</t>
+          <t>Deferred Income (unearned Revenue)</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Share Capital</t>
+          <t>Deferred Income</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>31010103</t>
+          <t>22060201</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>31010100</t>
+          <t>22060200</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -5742,54 +5774,50 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Dividends Paid</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Capital &amp; Reserves</t>
-        </is>
-      </c>
+          <t>Equity &amp; Reserve</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>31010200</t>
-        </is>
-      </c>
-      <c r="D182" s="3" t="inlineStr">
-        <is>
-          <t>31010000</t>
-        </is>
-      </c>
+          <t>30000000</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr"/>
       <c r="E182" t="n">
         <v>1</v>
       </c>
       <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
       <c r="H182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Shareholder Distributions</t>
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Equity &amp; Reserve</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Dividends Paid</t>
+          <t>Equity &amp; Reserve</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>31010104</t>
+          <t>31000000</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>31010200</t>
+          <t>30000000</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr"/>
@@ -5798,22 +5826,22 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Capital Grant</t>
+          <t>Capital &amp; Reserves</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Capital &amp; Reserves</t>
+          <t>Equity &amp; Reserve</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>31010300</t>
+          <t>31010000</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>31010000</t>
+          <t>31000000</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -5824,56 +5852,56 @@
       <c r="H184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Capital Grant</t>
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Share Capital</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Capital Grant</t>
+          <t>Capital &amp; Reserves</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>31010301</t>
+          <t>31010100</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>31010300</t>
+          <t>31010000</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>Directors Drawings</t>
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Ordinary Share Capital</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Capital &amp; Reserves</t>
+          <t>Share Capital</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>31010400</t>
+          <t>31010101</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>31010000</t>
+          <t>31010100</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
@@ -5882,22 +5910,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Directors Drawings</t>
+          <t>Preferred Shares</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Directors Drawings</t>
+          <t>Share Capital</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>31010401</t>
+          <t>31010102</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>31010400</t>
+          <t>31010100</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -5908,116 +5936,112 @@
       <c r="H187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="inlineStr">
-        <is>
-          <t>Retained Earnings</t>
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Share Premium</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Capital &amp; Reserves</t>
+          <t>Share Capital</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>31010500</t>
+          <t>31010103</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>31010000</t>
+          <t>31010100</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Retained Earnings</t>
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Dividends Paid</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Retained Earnings</t>
+          <t>Capital &amp; Reserves</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>31010501</t>
+          <t>31010200</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>31010500</t>
+          <t>31010000</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>0</v>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>Other Reservces</t>
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Shareholder Distributions</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Capital &amp; Reserves</t>
+          <t>Dividends Paid</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>31010600</t>
+          <t>31010104</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>31010000</t>
+          <t>31010200</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Revaluation Reserve</t>
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Capital Grant</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Other Reservces</t>
+          <t>Capital &amp; Reserves</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>31010601</t>
+          <t>31010300</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>31010600</t>
+          <t>31010000</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
@@ -6026,22 +6050,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Capital Reserve</t>
+          <t>Capital Grant</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Other Reservces</t>
+          <t>Capital Grant</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>31010602</t>
+          <t>31010301</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>31010600</t>
+          <t>31010300</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -6052,76 +6076,80 @@
       <c r="H192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Exchange Difference Reserve</t>
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Directors Drawings</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Other Reservces</t>
+          <t>Capital &amp; Reserves</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>31010603</t>
+          <t>31010400</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>31010600</t>
+          <t>31010000</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr"/>
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Directors Drawings</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Directors Drawings</t>
+        </is>
+      </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>40000000</t>
-        </is>
-      </c>
-      <c r="D194" s="3" t="inlineStr"/>
+          <t>31010401</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>31010400</t>
+        </is>
+      </c>
       <c r="E194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>Income</t>
-        </is>
-      </c>
+      <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Retained Earnings</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Capital &amp; Reserves</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>41000000</t>
+          <t>31010500</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>40000000</t>
+          <t>31010000</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -6132,52 +6160,56 @@
       <c r="H195" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>Stock Revenue</t>
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Retained Earnings</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>41010000</t>
+          <t>31010501</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>41000000</t>
+          <t>31010500</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1</v>
-      </c>
-      <c r="F196" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>Stock Revenue</t>
+          <t>Other Reservces</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Stock Revenue</t>
+          <t>Capital &amp; Reserves</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>41010100</t>
+          <t>31010600</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>41010000</t>
+          <t>31010000</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -6190,167 +6222,143 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Screen 18 Sales</t>
+          <t>Revaluation Reserve</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Stock Revenue</t>
+          <t>Other Reservces</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>41010101</t>
+          <t>31010601</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>41010100</t>
+          <t>31010600</t>
         </is>
       </c>
       <c r="E198" t="n">
         <v>0</v>
       </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>Income Account</t>
-        </is>
-      </c>
+      <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Screen 15 Sales</t>
+          <t>Capital Reserve</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Stock Revenue</t>
+          <t>Other Reservces</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>41010102</t>
+          <t>31010602</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>41010100</t>
+          <t>31010600</t>
         </is>
       </c>
       <c r="E199" t="n">
         <v>0</v>
       </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>Income Account</t>
-        </is>
-      </c>
+      <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Screen 12 Sales</t>
+          <t>Exchange Difference Reserve</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Stock Revenue</t>
+          <t>Other Reservces</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>41010103</t>
+          <t>31010603</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>41010100</t>
+          <t>31010600</t>
         </is>
       </c>
       <c r="E200" t="n">
         <v>0</v>
       </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>Income Account</t>
-        </is>
-      </c>
+      <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Undergrade Sales</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Stock Revenue</t>
-        </is>
-      </c>
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>41010104</t>
-        </is>
-      </c>
-      <c r="D201" s="3" t="inlineStr">
-        <is>
-          <t>41010100</t>
-        </is>
-      </c>
+          <t>40000000</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr"/>
       <c r="E201" t="n">
-        <v>0</v>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>Income Account</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
       <c r="H201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>By-product Sales</t>
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Stock Revenue</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>41010105</t>
+          <t>41000000</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>41010100</t>
+          <t>40000000</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>0</v>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>Income Account</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Stock Revenue</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6360,7 +6368,7 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>41020000</t>
+          <t>41010000</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -6378,22 +6386,22 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Stock Revenue</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Stock Revenue</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>41020100</t>
+          <t>41010100</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>41020000</t>
+          <t>41010000</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -6404,28 +6412,28 @@
       <c r="H204" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Interest Income</t>
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Robusta Sales</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Stock Revenue</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>41020101</t>
+          <t>41010110</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>41020100</t>
+          <t>41010100</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr"/>
@@ -6434,138 +6442,154 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Inventory Income</t>
+          <t>Robusta Screen 18 Sales</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Robusta Sales</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>41020102</t>
+          <t>41010111</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>41020100</t>
+          <t>41010110</t>
         </is>
       </c>
       <c r="E206" t="n">
         <v>0</v>
       </c>
-      <c r="F206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Income Account</t>
+        </is>
+      </c>
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Rounding Gain</t>
+          <t>Robusta Screen 15 Sales</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Robusta Sales</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>41020103</t>
+          <t>41010112</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>41020100</t>
+          <t>41010110</t>
         </is>
       </c>
       <c r="E207" t="n">
         <v>0</v>
       </c>
-      <c r="F207" t="inlineStr"/>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Income Account</t>
+        </is>
+      </c>
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Exchange Gain</t>
+          <t>Robusta Screen 12 Sales</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Robusta Sales</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>41020104</t>
+          <t>41010113</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>41020100</t>
+          <t>41010110</t>
         </is>
       </c>
       <c r="E208" t="n">
         <v>0</v>
       </c>
-      <c r="F208" t="inlineStr"/>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Income Account</t>
+        </is>
+      </c>
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Asset Disposal Gain</t>
+          <t>Robusta Undergrade Sales</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Robusta Sales</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>41020105</t>
+          <t>41010114</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>41020100</t>
+          <t>41010110</t>
         </is>
       </c>
       <c r="E209" t="n">
         <v>0</v>
       </c>
-      <c r="F209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Income Account</t>
+        </is>
+      </c>
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Other Income</t>
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Arabica Sales</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Stock Revenue</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>41020106</t>
+          <t>41010120</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>41020100</t>
+          <t>41010100</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr"/>
@@ -6574,350 +6598,354 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Other Discount Income</t>
+          <t>Arabica Screen 18 Sales</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Arabica Sales</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>41020107</t>
+          <t>41010121</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>41020100</t>
+          <t>41010120</t>
         </is>
       </c>
       <c r="E211" t="n">
         <v>0</v>
       </c>
-      <c r="F211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Income Account</t>
+        </is>
+      </c>
       <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>Cost of Goods</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr"/>
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Arabica Screen 15 Sales</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Arabica Sales</t>
+        </is>
+      </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>50000000</t>
-        </is>
-      </c>
-      <c r="D212" s="3" t="inlineStr"/>
+          <t>41010122</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>41010120</t>
+        </is>
+      </c>
       <c r="E212" t="n">
-        <v>1</v>
-      </c>
-      <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Income Account</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="inlineStr">
-        <is>
-          <t>Cost Of Goods Sold</t>
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Arabica Screen 12 Sales</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Cost of Goods</t>
+          <t>Arabica Sales</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>51000000</t>
+          <t>41010123</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>50000000</t>
+          <t>41010120</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1</v>
-      </c>
-      <c r="F213" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Income Account</t>
+        </is>
+      </c>
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>Direct Cost Of Goods Sold</t>
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Arabica Undergrade Sales</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Cost Of Goods Sold</t>
+          <t>Arabica Sales</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>51010000</t>
+          <t>41010124</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>51000000</t>
+          <t>41010120</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1</v>
-      </c>
-      <c r="F214" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Income Account</t>
+        </is>
+      </c>
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>Cost Of Sales</t>
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>By-product Sales</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Direct Cost Of Goods Sold</t>
+          <t>Stock Revenue</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>51010100</t>
+          <t>41010130</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>51010000</t>
+          <t>41010100</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1</v>
-      </c>
-      <c r="F215" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Income Account</t>
+        </is>
+      </c>
       <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Screen 18 Cost of Sales</t>
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Cost Of Sales</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>51010101</t>
+          <t>41020000</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>51010100</t>
+          <t>41000000</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>0</v>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>Cost of Goods Sold</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Screen 15 Cost of Sales</t>
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Cost Of Sales</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>51010102</t>
+          <t>41020100</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>51010100</t>
+          <t>41020000</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>0</v>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>Cost of Goods Sold</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Screen 12 Cost of Sales</t>
+          <t>Interest Income</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Cost Of Sales</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>51010103</t>
+          <t>41020101</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>51010100</t>
+          <t>41020100</t>
         </is>
       </c>
       <c r="E218" t="n">
         <v>0</v>
       </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>Cost of Goods Sold</t>
-        </is>
-      </c>
+      <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Undergrade Cost of Sales</t>
+          <t>Inventory Income</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Cost Of Sales</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>51010104</t>
+          <t>41020102</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>51010100</t>
+          <t>41020100</t>
         </is>
       </c>
       <c r="E219" t="n">
         <v>0</v>
       </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>Cost of Goods Sold</t>
-        </is>
-      </c>
+      <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>By-product Cost of Sales</t>
+          <t>Rounding Gain</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Cost Of Sales</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>51010105</t>
+          <t>41020103</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>51010100</t>
+          <t>41020100</t>
         </is>
       </c>
       <c r="E220" t="n">
         <v>0</v>
       </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>Cost of Goods Sold</t>
-        </is>
-      </c>
+      <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>Indirect Cost Of Goods Sold</t>
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Exchange Gain</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Cost Of Goods Sold</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>51020000</t>
+          <t>41020104</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>51000000</t>
+          <t>41020100</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>Lost In Transit</t>
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Asset Disposal Gain</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Indirect Cost Of Goods Sold</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>51010300</t>
+          <t>41020105</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>51020000</t>
+          <t>41020100</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr"/>
@@ -6926,22 +6954,22 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Lost In Transit</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Lost In Transit</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>51010301</t>
+          <t>41020106</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
-          <t>51010300</t>
+          <t>41020100</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -6952,304 +6980,316 @@
       <c r="H223" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>Stock Adjustments</t>
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Other Discount Income</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Indirect Cost Of Goods Sold</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>51020200</t>
+          <t>41020107</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>51020000</t>
+          <t>41020100</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>Stock Adjustment Account</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Stock Adjustments</t>
-        </is>
-      </c>
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Cost of Goods</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>51010201</t>
-        </is>
-      </c>
-      <c r="D225" s="3" t="inlineStr">
-        <is>
-          <t>51020200</t>
-        </is>
-      </c>
+          <t>50000000</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr"/>
       <c r="E225" t="n">
-        <v>0</v>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>Stock Adjustment</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
       <c r="H225" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>Stock Differences Account</t>
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Cost Of Goods Sold</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Stock Adjustments</t>
+          <t>Cost of Goods</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>51010202</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>51020200</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Price Differences Account</t>
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Direct Cost Of Goods Sold</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Stock Adjustments</t>
+          <t>Cost Of Goods Sold</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>51010203</t>
+          <t>51010000</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>51020200</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>Expiry</t>
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Cost Of Sales</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Stock Adjustments</t>
+          <t>Direct Cost Of Goods Sold</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>51010205</t>
+          <t>51010100</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>51020200</t>
+          <t>51010000</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>Damanged Goods</t>
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Robusta Cost of Sales</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Stock Adjustments</t>
+          <t>Cost Of Sales</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>51010206</t>
+          <t>51010110</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>51020200</t>
+          <t>51010100</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>Discount Allowed</t>
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Robusta Screen 18 Cost of Sales</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Cost Of Goods Sold</t>
+          <t>Robusta Cost of Sales</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>52010000</t>
+          <t>51010111</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>51000000</t>
+          <t>51010110</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>1</v>
-      </c>
-      <c r="F230" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Cost of Goods Sold</t>
+        </is>
+      </c>
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="inlineStr">
-        <is>
-          <t>Discount Allowed</t>
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Robusta Screen 15 Cost of Sales</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Discount Allowed</t>
+          <t>Robusta Cost of Sales</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>52010100</t>
+          <t>51010112</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>52010000</t>
+          <t>51010110</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>1</v>
-      </c>
-      <c r="F231" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Cost of Goods Sold</t>
+        </is>
+      </c>
       <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Discount Allowed</t>
+          <t>Robusta Screen 12 Cost of Sales</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Discount Allowed</t>
+          <t>Robusta Cost of Sales</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>52010101</t>
+          <t>51010113</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>52010100</t>
+          <t>51010110</t>
         </is>
       </c>
       <c r="E232" t="n">
         <v>0</v>
       </c>
-      <c r="F232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Cost of Goods Sold</t>
+        </is>
+      </c>
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="inlineStr">
-        <is>
-          <t>Operating Cost</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr"/>
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Robusta Undergrade Cost of Sales</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Robusta Cost of Sales</t>
+        </is>
+      </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>60000000</t>
-        </is>
-      </c>
-      <c r="D233" s="3" t="inlineStr"/>
+          <t>51010114</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>51010110</t>
+        </is>
+      </c>
       <c r="E233" t="n">
-        <v>1</v>
-      </c>
-      <c r="F233" t="inlineStr"/>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Cost of Goods Sold</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Arabica Cost of Sales</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Cost Of Sales</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>61000000</t>
+          <t>51010120</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>60000000</t>
+          <t>51010100</t>
         </is>
       </c>
       <c r="E234" t="n">
@@ -7260,196 +7300,216 @@
       <c r="H234" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="inlineStr">
-        <is>
-          <t>Operating Cost</t>
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Arabica Screen 18 Cost of Sales</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Arabica Cost of Sales</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>61010000</t>
+          <t>51010121</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
-          <t>61000000</t>
+          <t>51010120</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>1</v>
-      </c>
-      <c r="F235" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Cost of Goods Sold</t>
+        </is>
+      </c>
       <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>Operating Cost</t>
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Arabica Screen 15 Cost of Sales</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Arabica Cost of Sales</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>61010100</t>
+          <t>51010122</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>61010000</t>
+          <t>51010120</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>1</v>
-      </c>
-      <c r="F236" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Cost of Goods Sold</t>
+        </is>
+      </c>
       <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Bank&amp;Finance Costs</t>
+          <t>Arabica Screen 12 Cost of Sales</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Arabica Cost of Sales</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>61010101</t>
+          <t>51010123</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
-          <t>61010100</t>
+          <t>51010120</t>
         </is>
       </c>
       <c r="E237" t="n">
         <v>0</v>
       </c>
-      <c r="F237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Cost of Goods Sold</t>
+        </is>
+      </c>
       <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Administrative Expenses</t>
+          <t>Arabica Undergrade Cost of Sales</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Arabica Cost of Sales</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>61010102</t>
+          <t>51010124</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>61010100</t>
+          <t>51010120</t>
         </is>
       </c>
       <c r="E238" t="n">
         <v>0</v>
       </c>
-      <c r="F238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Cost of Goods Sold</t>
+        </is>
+      </c>
       <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Bad Debts</t>
+          <t>By-product Cost of Sales</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Cost Of Sales</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>61010103</t>
+          <t>51010130</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>61010100</t>
+          <t>51010100</t>
         </is>
       </c>
       <c r="E239" t="n">
         <v>0</v>
       </c>
-      <c r="F239" t="inlineStr"/>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Cost of Goods Sold</t>
+        </is>
+      </c>
       <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>Commission - Coffee Agents</t>
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Indirect Cost Of Goods Sold</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Cost Of Goods Sold</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>61010105</t>
+          <t>51020000</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>61010100</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>Commission on Delivery</t>
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>Lost In Transit</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Indirect Cost Of Goods Sold</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>61010106</t>
+          <t>51010300</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
         <is>
-          <t>61010100</t>
+          <t>51020000</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr"/>
@@ -7458,22 +7518,22 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>DAMAGES AND EXPIRES</t>
+          <t>Lost In Transit</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Lost In Transit</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>61010107</t>
+          <t>51010301</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>61010100</t>
+          <t>51010300</t>
         </is>
       </c>
       <c r="E242" t="n">
@@ -7484,28 +7544,28 @@
       <c r="H242" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>Damages&amp;Loss</t>
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Stock Adjustments</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Indirect Cost Of Goods Sold</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>61010108</t>
+          <t>51020200</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>61010100</t>
+          <t>51020000</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr"/>
@@ -7514,50 +7574,54 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Delivery Cost to Customers</t>
+          <t>Stock Adjustment Account</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Stock Adjustments</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>61010109</t>
+          <t>51010201</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>61010100</t>
+          <t>51020200</t>
         </is>
       </c>
       <c r="E244" t="n">
         <v>0</v>
       </c>
-      <c r="F244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Stock Adjustment</t>
+        </is>
+      </c>
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Director's Allowances</t>
+          <t>Stock Differences Account</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Stock Adjustments</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>61010110</t>
+          <t>51010202</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>61010100</t>
+          <t>51020200</t>
         </is>
       </c>
       <c r="E245" t="n">
@@ -7570,22 +7634,22 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>DONATIONS</t>
+          <t>Price Differences Account</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Stock Adjustments</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>61010111</t>
+          <t>51010203</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>61010100</t>
+          <t>51020200</t>
         </is>
       </c>
       <c r="E246" t="n">
@@ -7598,22 +7662,22 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Electricity Bills</t>
+          <t>Expiry</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Stock Adjustments</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>61010112</t>
+          <t>51010205</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
-          <t>61010100</t>
+          <t>51020200</t>
         </is>
       </c>
       <c r="E247" t="n">
@@ -7626,22 +7690,22 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Handling&amp;Agency Fees</t>
+          <t>Damanged Goods</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Stock Adjustments</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>61010113</t>
+          <t>51010206</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>61010100</t>
+          <t>51020200</t>
         </is>
       </c>
       <c r="E248" t="n">
@@ -7652,56 +7716,56 @@
       <c r="H248" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>Income Tax</t>
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Discount Allowed</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Cost Of Goods Sold</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>61010114</t>
+          <t>52010000</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>61010100</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>Insurance</t>
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Discount Allowed</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Discount Allowed</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>61010115</t>
+          <t>52010100</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>61010100</t>
+          <t>52010000</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr"/>
@@ -7710,22 +7774,22 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Legal Fees</t>
+          <t>Discount Allowed</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Discount Allowed</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>61010116</t>
+          <t>52010101</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
-          <t>61010100</t>
+          <t>52010100</t>
         </is>
       </c>
       <c r="E251" t="n">
@@ -7736,37 +7800,33 @@
       <c r="H251" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>Licences&amp; Permits</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
+      <c r="A252" s="2" t="inlineStr">
         <is>
           <t>Operating Cost</t>
         </is>
       </c>
+      <c r="B252" t="inlineStr"/>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>61010117</t>
-        </is>
-      </c>
-      <c r="D252" s="3" t="inlineStr">
-        <is>
-          <t>61010100</t>
-        </is>
-      </c>
+          <t>60000000</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr"/>
       <c r="E252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr"/>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
       <c r="H252" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>LOSSES</t>
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7776,25 +7836,25 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>61010118</t>
+          <t>61000000</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
-          <t>61010100</t>
+          <t>60000000</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>Marketing Expenses</t>
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7804,25 +7864,25 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>61010119</t>
+          <t>61010000</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>61010100</t>
+          <t>61000000</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>Miscellenous Exp</t>
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7832,16 +7892,16 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>61010120</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>61010100</t>
+          <t>61010000</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr"/>
@@ -7850,7 +7910,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Motorbike Fuel &amp;Maintenance</t>
+          <t>Bank&amp;Finance Costs</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -7860,7 +7920,7 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>61010121</t>
+          <t>61010101</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
@@ -7878,7 +7938,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>NSSF Expenses</t>
+          <t>Administrative Expenses</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -7888,7 +7948,7 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>61010122</t>
+          <t>61010102</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
@@ -7906,7 +7966,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Office Expenses</t>
+          <t>Bad Debts</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -7916,7 +7976,7 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>61010123</t>
+          <t>61010103</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
@@ -7934,7 +7994,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Office Repairs &amp;Maintenance</t>
+          <t>Commission - Coffee Agents</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -7944,7 +8004,7 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>61010124</t>
+          <t>61010105</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
@@ -7962,7 +8022,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Office Transport</t>
+          <t>Commission on Delivery</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -7972,7 +8032,7 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>61010125</t>
+          <t>61010106</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
@@ -7990,7 +8050,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>DAMAGES AND EXPIRES</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -8000,7 +8060,7 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>61010126</t>
+          <t>61010107</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
@@ -8018,7 +8078,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>PAYE</t>
+          <t>Damages&amp;Loss</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -8028,7 +8088,7 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>61010127</t>
+          <t>61010108</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -8046,7 +8106,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Rent Exp.</t>
+          <t>Delivery Cost to Customers</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -8056,7 +8116,7 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>61010128</t>
+          <t>61010109</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
@@ -8074,7 +8134,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Salaries &amp; Wages</t>
+          <t>Director's Allowances</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -8084,7 +8144,7 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>61010129</t>
+          <t>61010110</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
@@ -8102,7 +8162,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Security Expenses</t>
+          <t>DONATIONS</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -8112,7 +8172,7 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>61010130</t>
+          <t>61010111</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
@@ -8130,7 +8190,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Staff Allowance-Lunch</t>
+          <t>Electricity Bills</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -8140,7 +8200,7 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>61010131</t>
+          <t>61010112</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
@@ -8158,7 +8218,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Staff Allowances-Transport</t>
+          <t>Handling&amp;Agency Fees</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -8168,7 +8228,7 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>61010132</t>
+          <t>61010113</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
@@ -8186,7 +8246,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Staff Bonus</t>
+          <t>Income Tax</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -8196,7 +8256,7 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>61010133</t>
+          <t>61010114</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
@@ -8214,7 +8274,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Staff Medical Expenses</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -8224,7 +8284,7 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>61010134</t>
+          <t>61010115</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
@@ -8242,7 +8302,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Staff Uniforms</t>
+          <t>Legal Fees</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -8252,7 +8312,7 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>61010135</t>
+          <t>61010116</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
@@ -8270,7 +8330,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Staff Welfare</t>
+          <t>Licences&amp; Permits</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -8280,7 +8340,7 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>61010136</t>
+          <t>61010117</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
@@ -8298,7 +8358,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Stationery Expenses</t>
+          <t>LOSSES</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -8308,7 +8368,7 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>61010137</t>
+          <t>61010118</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
@@ -8326,7 +8386,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Telephone&amp;Internet Exp</t>
+          <t>Marketing Expenses</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -8336,7 +8396,7 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>61010138</t>
+          <t>61010119</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
@@ -8354,7 +8414,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Trading Licence &amp;Permits</t>
+          <t>Miscellenous Exp</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -8364,7 +8424,7 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>61010139</t>
+          <t>61010120</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
@@ -8382,7 +8442,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Travelling Expenses</t>
+          <t>Motorbike Fuel &amp;Maintenance</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -8392,7 +8452,7 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>61010140</t>
+          <t>61010121</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
@@ -8410,7 +8470,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Water Bills</t>
+          <t>NSSF Expenses</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -8420,7 +8480,7 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>61010141</t>
+          <t>61010122</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
@@ -8438,7 +8498,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Web Hosting</t>
+          <t>Office Expenses</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -8448,7 +8508,7 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>61010142</t>
+          <t>61010123</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
@@ -8464,9 +8524,9 @@
       <c r="H277" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="inlineStr">
-        <is>
-          <t>Finance Cost</t>
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Office Repairs &amp;Maintenance</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -8476,16 +8536,16 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>63010200</t>
+          <t>61010124</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>61010000</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F278" t="inlineStr"/>
       <c r="G278" t="inlineStr"/>
@@ -8494,22 +8554,22 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Bank Charges</t>
+          <t>Office Transport</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Finance Cost</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>63010101</t>
+          <t>61010125</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
         <is>
-          <t>63010200</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="E279" t="n">
@@ -8522,22 +8582,22 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Momo/Easy Pay Charges</t>
+          <t>Packaging</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Finance Cost</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>63010102</t>
+          <t>61010126</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>63010200</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="E280" t="n">
@@ -8550,22 +8610,22 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Interest Expense</t>
+          <t>PAYE</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Finance Cost</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>63010103</t>
+          <t>61010127</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
         <is>
-          <t>63010200</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="E281" t="n">
@@ -8578,22 +8638,22 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Exchange Loss</t>
+          <t>Rent Exp.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Finance Cost</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>63010104</t>
+          <t>61010128</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>63010200</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="E282" t="n">
@@ -8606,22 +8666,22 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Unrealized Loss On Exchange Rate Differences</t>
+          <t>Salaries &amp; Wages</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Finance Cost</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>63010105</t>
+          <t>61010129</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
         <is>
-          <t>63010200</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="E283" t="n">
@@ -8634,54 +8694,50 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Rounding Loss</t>
+          <t>Security Expenses</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Finance Cost</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>63010106</t>
+          <t>61010130</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>63010200</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="E284" t="n">
         <v>0</v>
       </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>Round Off</t>
-        </is>
-      </c>
+      <c r="F284" t="inlineStr"/>
       <c r="G284" t="inlineStr"/>
       <c r="H284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Service Charge</t>
+          <t>Staff Allowance-Lunch</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Finance Cost</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>63010107</t>
+          <t>61010131</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
         <is>
-          <t>63010200</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="E285" t="n">
@@ -8694,22 +8750,22 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Od Interest/service Change</t>
+          <t>Staff Allowances-Transport</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Finance Cost</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>63010108</t>
+          <t>61010132</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>63010200</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="E286" t="n">
@@ -8722,22 +8778,22 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Fake Notes</t>
+          <t>Staff Bonus</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Finance Cost</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>63010109</t>
+          <t>61010133</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
         <is>
-          <t>63010200</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="E287" t="n">
@@ -8750,22 +8806,22 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Loan Processing fees</t>
+          <t>Staff Medical Expenses</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Finance Cost</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>63010110</t>
+          <t>61010134</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>63010200</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="E288" t="n">
@@ -8776,9 +8832,9 @@
       <c r="H288" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="inlineStr">
-        <is>
-          <t>Depreciation Expense</t>
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Staff Uniforms</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -8788,16 +8844,16 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>63010300</t>
+          <t>61010135</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
         <is>
-          <t>61010000</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F289" t="inlineStr"/>
       <c r="G289" t="inlineStr"/>
@@ -8806,167 +8862,147 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Depreciation Expense - Buildings</t>
+          <t>Staff Welfare</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Depreciation Expense</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>63010301</t>
+          <t>61010136</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>63010300</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="E290" t="n">
         <v>0</v>
       </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+      <c r="F290" t="inlineStr"/>
       <c r="G290" t="inlineStr"/>
       <c r="H290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Depreciation Expense -Furniture &amp; Fittings</t>
+          <t>Stationery Expenses</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Depreciation Expense</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>63010302</t>
+          <t>61010137</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
         <is>
-          <t>63010300</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="E291" t="n">
         <v>0</v>
       </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+      <c r="F291" t="inlineStr"/>
       <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Depreciation Expense - Machinery &amp; Equipment</t>
+          <t>Telephone&amp;Internet Exp</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Depreciation Expense</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>63010303</t>
+          <t>61010138</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>63010300</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="E292" t="n">
         <v>0</v>
       </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+      <c r="F292" t="inlineStr"/>
       <c r="G292" t="inlineStr"/>
       <c r="H292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Depreciation Expense - Motor Vehicles</t>
+          <t>Trading Licence &amp;Permits</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Depreciation Expense</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>63010304</t>
+          <t>61010139</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
         <is>
-          <t>63010300</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="E293" t="n">
         <v>0</v>
       </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+      <c r="F293" t="inlineStr"/>
       <c r="G293" t="inlineStr"/>
       <c r="H293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Computers &amp; Data Processing Equip</t>
+          <t>Travelling Expenses</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Depreciation Expense</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>63010305</t>
+          <t>61010140</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>63010300</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="E294" t="n">
         <v>0</v>
       </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+      <c r="F294" t="inlineStr"/>
       <c r="G294" t="inlineStr"/>
       <c r="H294" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="inlineStr">
-        <is>
-          <t>Other Expenses</t>
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Water Bills</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -8976,16 +9012,16 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>63010500</t>
+          <t>61010141</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
         <is>
-          <t>61010000</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F295" t="inlineStr"/>
       <c r="G295" t="inlineStr"/>
@@ -8994,22 +9030,22 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Penalties &amp; Fines</t>
+          <t>Web Hosting</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>63010501</t>
+          <t>61010142</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
         <is>
-          <t>63010500</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="E296" t="n">
@@ -9020,28 +9056,28 @@
       <c r="H296" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>Legal Expenses</t>
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>Finance Cost</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>63010502</t>
+          <t>63010200</t>
         </is>
       </c>
       <c r="D297" s="3" t="inlineStr">
         <is>
-          <t>63010500</t>
+          <t>61010000</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F297" t="inlineStr"/>
       <c r="G297" t="inlineStr"/>
@@ -9050,22 +9086,22 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Customs Penalty Tax</t>
+          <t>Bank Charges</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Finance Cost</t>
         </is>
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>63010503</t>
+          <t>63010101</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>63010500</t>
+          <t>63010200</t>
         </is>
       </c>
       <c r="E298" t="n">
@@ -9078,22 +9114,22 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>Momo/Easy Pay Charges</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Finance Cost</t>
         </is>
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>63010504</t>
+          <t>63010102</t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr">
         <is>
-          <t>63010500</t>
+          <t>63010200</t>
         </is>
       </c>
       <c r="E299" t="n">
@@ -9106,22 +9142,22 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Realized Loss On Exchange Rate Differences</t>
+          <t>Interest Expense</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Finance Cost</t>
         </is>
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>63010505</t>
+          <t>63010103</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>63010500</t>
+          <t>63010200</t>
         </is>
       </c>
       <c r="E300" t="n">
@@ -9134,22 +9170,22 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Unrealized Loss On Exchange Rate Differences</t>
+          <t>Exchange Loss</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Finance Cost</t>
         </is>
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>63010506</t>
+          <t>63010104</t>
         </is>
       </c>
       <c r="D301" s="3" t="inlineStr">
         <is>
-          <t>63010500</t>
+          <t>63010200</t>
         </is>
       </c>
       <c r="E301" t="n">
@@ -9162,22 +9198,22 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Loss / Gain On Asset Disposal</t>
+          <t>Unrealized Loss On Exchange Rate Differences</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Finance Cost</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>63010507</t>
+          <t>63010105</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>63010500</t>
+          <t>63010200</t>
         </is>
       </c>
       <c r="E302" t="n">
@@ -9190,54 +9226,58 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Tax Penalties</t>
+          <t>Rounding Loss</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Finance Cost</t>
         </is>
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>63010508</t>
+          <t>63010106</t>
         </is>
       </c>
       <c r="D303" s="3" t="inlineStr">
         <is>
-          <t>63010500</t>
+          <t>63010200</t>
         </is>
       </c>
       <c r="E303" t="n">
         <v>0</v>
       </c>
-      <c r="F303" t="inlineStr"/>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Round Off</t>
+        </is>
+      </c>
       <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="inlineStr">
-        <is>
-          <t>Amortization Expense</t>
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Service Charge</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Finance Cost</t>
         </is>
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>63020400</t>
+          <t>63010107</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
         <is>
-          <t>61010000</t>
+          <t>63010200</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="inlineStr"/>
@@ -9246,110 +9286,106 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Amortization Expense - Software &amp; Licenses</t>
+          <t>Od Interest/service Change</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Amortization Expense</t>
+          <t>Finance Cost</t>
         </is>
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>63020401</t>
+          <t>63010108</t>
         </is>
       </c>
       <c r="D305" s="3" t="inlineStr">
         <is>
-          <t>63020400</t>
+          <t>63010200</t>
         </is>
       </c>
       <c r="E305" t="n">
         <v>0</v>
       </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+      <c r="F305" t="inlineStr"/>
       <c r="G305" t="inlineStr"/>
       <c r="H305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Amortization Expense - Goodwill</t>
+          <t>Fake Notes</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Amortization Expense</t>
+          <t>Finance Cost</t>
         </is>
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>63020402</t>
+          <t>63010109</t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr">
         <is>
-          <t>63020400</t>
+          <t>63010200</t>
         </is>
       </c>
       <c r="E306" t="n">
         <v>0</v>
       </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+      <c r="F306" t="inlineStr"/>
       <c r="G306" t="inlineStr"/>
       <c r="H306" t="inlineStr"/>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="inlineStr">
-        <is>
-          <t>Opening Balance</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr"/>
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Loan Processing fees</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Finance Cost</t>
+        </is>
+      </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>90000000</t>
-        </is>
-      </c>
-      <c r="D307" s="3" t="inlineStr"/>
+          <t>63010110</t>
+        </is>
+      </c>
+      <c r="D307" s="3" t="inlineStr">
+        <is>
+          <t>63010200</t>
+        </is>
+      </c>
       <c r="E307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F307" t="inlineStr"/>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>Liability</t>
-        </is>
-      </c>
+      <c r="G307" t="inlineStr"/>
       <c r="H307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>Opening Balance</t>
+          <t>Depreciation Expense</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Opening Balance</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t>90100000</t>
+          <t>63010300</t>
         </is>
       </c>
       <c r="D308" s="3" t="inlineStr">
         <is>
-          <t>90000000</t>
+          <t>61010000</t>
         </is>
       </c>
       <c r="E308" t="n">
@@ -9360,52 +9396,56 @@
       <c r="H308" t="inlineStr"/>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="inlineStr">
-        <is>
-          <t>Opening Balance</t>
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Depreciation Expense - Buildings</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Opening Balance</t>
+          <t>Depreciation Expense</t>
         </is>
       </c>
       <c r="C309" s="3" t="inlineStr">
         <is>
-          <t>90101000</t>
+          <t>63010301</t>
         </is>
       </c>
       <c r="D309" s="3" t="inlineStr">
         <is>
-          <t>90100000</t>
+          <t>63010300</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>1</v>
-      </c>
-      <c r="F309" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Opening Balance</t>
+          <t>Depreciation Expense -Furniture &amp; Fittings</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Opening Balance</t>
+          <t>Depreciation Expense</t>
         </is>
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>901010100</t>
+          <t>63010302</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
         <is>
-          <t>90101000</t>
+          <t>63010300</t>
         </is>
       </c>
       <c r="E310" t="n">
@@ -9413,11 +9453,563 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Temporary</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="G310" t="inlineStr"/>
       <c r="H310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Depreciation Expense - Machinery &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Depreciation Expense</t>
+        </is>
+      </c>
+      <c r="C311" s="3" t="inlineStr">
+        <is>
+          <t>63010303</t>
+        </is>
+      </c>
+      <c r="D311" s="3" t="inlineStr">
+        <is>
+          <t>63010300</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>0</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr"/>
+      <c r="H311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Depreciation Expense - Motor Vehicles</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Depreciation Expense</t>
+        </is>
+      </c>
+      <c r="C312" s="3" t="inlineStr">
+        <is>
+          <t>63010304</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="inlineStr">
+        <is>
+          <t>63010300</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>0</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr"/>
+      <c r="H312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Computers &amp; Data Processing Equip</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Depreciation Expense</t>
+        </is>
+      </c>
+      <c r="C313" s="3" t="inlineStr">
+        <is>
+          <t>63010305</t>
+        </is>
+      </c>
+      <c r="D313" s="3" t="inlineStr">
+        <is>
+          <t>63010300</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>0</v>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr"/>
+      <c r="H313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="C314" s="3" t="inlineStr">
+        <is>
+          <t>63010500</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>61010000</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>1</v>
+      </c>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr"/>
+      <c r="H314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Penalties &amp; Fines</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="C315" s="3" t="inlineStr">
+        <is>
+          <t>63010501</t>
+        </is>
+      </c>
+      <c r="D315" s="3" t="inlineStr">
+        <is>
+          <t>63010500</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>0</v>
+      </c>
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="inlineStr"/>
+      <c r="H315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Legal Expenses</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="C316" s="3" t="inlineStr">
+        <is>
+          <t>63010502</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>63010500</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>0</v>
+      </c>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr"/>
+      <c r="H316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Customs Penalty Tax</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="C317" s="3" t="inlineStr">
+        <is>
+          <t>63010503</t>
+        </is>
+      </c>
+      <c r="D317" s="3" t="inlineStr">
+        <is>
+          <t>63010500</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>0</v>
+      </c>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr"/>
+      <c r="H317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Donations</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="C318" s="3" t="inlineStr">
+        <is>
+          <t>63010504</t>
+        </is>
+      </c>
+      <c r="D318" s="3" t="inlineStr">
+        <is>
+          <t>63010500</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>0</v>
+      </c>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr"/>
+      <c r="H318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Realized Loss On Exchange Rate Differences</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="C319" s="3" t="inlineStr">
+        <is>
+          <t>63010505</t>
+        </is>
+      </c>
+      <c r="D319" s="3" t="inlineStr">
+        <is>
+          <t>63010500</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>0</v>
+      </c>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr"/>
+      <c r="H319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Unrealized Loss On Exchange Rate Differences</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="C320" s="3" t="inlineStr">
+        <is>
+          <t>63010506</t>
+        </is>
+      </c>
+      <c r="D320" s="3" t="inlineStr">
+        <is>
+          <t>63010500</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>0</v>
+      </c>
+      <c r="F320" t="inlineStr"/>
+      <c r="G320" t="inlineStr"/>
+      <c r="H320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Loss / Gain On Asset Disposal</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="C321" s="3" t="inlineStr">
+        <is>
+          <t>63010507</t>
+        </is>
+      </c>
+      <c r="D321" s="3" t="inlineStr">
+        <is>
+          <t>63010500</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>0</v>
+      </c>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr"/>
+      <c r="H321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Tax Penalties</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="C322" s="3" t="inlineStr">
+        <is>
+          <t>63010508</t>
+        </is>
+      </c>
+      <c r="D322" s="3" t="inlineStr">
+        <is>
+          <t>63010500</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>0</v>
+      </c>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr"/>
+      <c r="H322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>Amortization Expense</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="C323" s="3" t="inlineStr">
+        <is>
+          <t>63020400</t>
+        </is>
+      </c>
+      <c r="D323" s="3" t="inlineStr">
+        <is>
+          <t>61010000</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>1</v>
+      </c>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr"/>
+      <c r="H323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Amortization Expense - Software &amp; Licenses</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Amortization Expense</t>
+        </is>
+      </c>
+      <c r="C324" s="3" t="inlineStr">
+        <is>
+          <t>63020401</t>
+        </is>
+      </c>
+      <c r="D324" s="3" t="inlineStr">
+        <is>
+          <t>63020400</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>0</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr"/>
+      <c r="H324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Amortization Expense - Goodwill</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Amortization Expense</t>
+        </is>
+      </c>
+      <c r="C325" s="3" t="inlineStr">
+        <is>
+          <t>63020402</t>
+        </is>
+      </c>
+      <c r="D325" s="3" t="inlineStr">
+        <is>
+          <t>63020400</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>0</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr"/>
+      <c r="H325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>Opening Balance</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr"/>
+      <c r="C326" s="3" t="inlineStr">
+        <is>
+          <t>90000000</t>
+        </is>
+      </c>
+      <c r="D326" s="3" t="inlineStr"/>
+      <c r="E326" t="n">
+        <v>1</v>
+      </c>
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Liability</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>Opening Balance</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Opening Balance</t>
+        </is>
+      </c>
+      <c r="C327" s="3" t="inlineStr">
+        <is>
+          <t>90100000</t>
+        </is>
+      </c>
+      <c r="D327" s="3" t="inlineStr">
+        <is>
+          <t>90000000</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>1</v>
+      </c>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr"/>
+      <c r="H327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>Opening Balance</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Opening Balance</t>
+        </is>
+      </c>
+      <c r="C328" s="3" t="inlineStr">
+        <is>
+          <t>90101000</t>
+        </is>
+      </c>
+      <c r="D328" s="3" t="inlineStr">
+        <is>
+          <t>90100000</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>1</v>
+      </c>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr"/>
+      <c r="H328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Opening Balance</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Opening Balance</t>
+        </is>
+      </c>
+      <c r="C329" s="3" t="inlineStr">
+        <is>
+          <t>901010100</t>
+        </is>
+      </c>
+      <c r="D329" s="3" t="inlineStr">
+        <is>
+          <t>90101000</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>0</v>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Temporary</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr"/>
+      <c r="H329" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/demo_import/00_chart_of_accounts.xlsx
+++ b/demo_import/00_chart_of_accounts.xlsx
@@ -4267,11 +4267,7 @@
       <c r="E129" t="n">
         <v>0</v>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Payable</t>
-        </is>
-      </c>
+      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
@@ -4331,11 +4327,7 @@
       <c r="E131" t="n">
         <v>0</v>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Payable</t>
-        </is>
-      </c>
+      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>

--- a/demo_import/00_chart_of_accounts.xlsx
+++ b/demo_import/00_chart_of_accounts.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H329"/>
+  <dimension ref="A1:H330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -2154,7 +2154,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Stock Account</t>
+          <t>Raw Material Stock</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2184,19 +2184,19 @@
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Robusta Stock</t>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Robusta FAQ Stock</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Stock Account</t>
+          <t>Raw Material Stock</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>12010110</t>
+          <t>12010101</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -2205,7 +2205,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2218,22 +2218,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Robusta FAQ Stock</t>
+          <t>Arabica Parchment Stock</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Robusta Stock</t>
+          <t>Raw Material Stock</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>12010111</t>
+          <t>12010102</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>12010110</t>
+          <t>12010100</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -2248,28 +2248,28 @@
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Robusta Screen 18 Stock</t>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Finished Product Stock</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Robusta Stock</t>
+          <t>Stock Account</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>12010112</t>
+          <t>12010300</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>12010110</t>
+          <t>12010000</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2280,28 +2280,28 @@
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Robusta Screen 15 Stock</t>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Robusta Finished Stock</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Robusta Stock</t>
+          <t>Finished Product Stock</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>12010113</t>
+          <t>12010310</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>12010110</t>
+          <t>12010300</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2314,22 +2314,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Robusta Screen 12 Stock</t>
+          <t>Robusta Screen 18 Stock</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Robusta Stock</t>
+          <t>Robusta Finished Stock</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>12010114</t>
+          <t>12010311</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>12010110</t>
+          <t>12010310</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2346,22 +2346,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Robusta Undergrades Stock</t>
+          <t>Robusta Screen 15 Stock</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Robusta Stock</t>
+          <t>Robusta Finished Stock</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>12010115</t>
+          <t>12010312</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>12010110</t>
+          <t>12010310</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2376,28 +2376,28 @@
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Arabica Stock</t>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Robusta Screen 12 Stock</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Stock Account</t>
+          <t>Robusta Finished Stock</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>12010120</t>
+          <t>12010313</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>12010100</t>
+          <t>12010310</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2410,22 +2410,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Arabica Parchment Stock</t>
+          <t>Robusta Undergrades Stock</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Arabica Stock</t>
+          <t>Robusta Finished Stock</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>12010121</t>
+          <t>12010314</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>12010120</t>
+          <t>12010310</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2440,28 +2440,28 @@
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Arabica Screen 18 Stock</t>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Arabica Finished Stock</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Arabica Stock</t>
+          <t>Finished Product Stock</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>12010122</t>
+          <t>12010320</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>12010120</t>
+          <t>12010300</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2474,22 +2474,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Arabica Screen 15 Stock</t>
+          <t>Arabica Screen 18 Stock</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Arabica Stock</t>
+          <t>Arabica Finished Stock</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>12010123</t>
+          <t>12010321</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>12010120</t>
+          <t>12010320</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2506,22 +2506,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Arabica Screen 12 Stock</t>
+          <t>Arabica Screen 15 Stock</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Arabica Stock</t>
+          <t>Arabica Finished Stock</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>12010124</t>
+          <t>12010322</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>12010120</t>
+          <t>12010320</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2538,22 +2538,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Arabica Undergrades Stock</t>
+          <t>Arabica Screen 12 Stock</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Arabica Stock</t>
+          <t>Arabica Finished Stock</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>12010125</t>
+          <t>12010323</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>12010120</t>
+          <t>12010320</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2570,22 +2570,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>By-products Stock</t>
+          <t>Arabica Undergrades Stock</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Stock Account</t>
+          <t>Arabica Finished Stock</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>12010130</t>
+          <t>12010324</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>12010100</t>
+          <t>12010320</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2600,148 +2600,148 @@
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Damages/Expiries</t>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>By-products Stock</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Stock Account</t>
+          <t>Finished Product Stock</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>12010200</t>
+          <t>12010330</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>12010000</t>
+          <t>12010300</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Inventory - Damages/Expired</t>
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Damages/Expiries</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Damages/Expiries</t>
+          <t>Stock Account</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>12010501</t>
+          <t>12010200</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>12010200</t>
+          <t>12010000</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>Trade Receivables</t>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Inventory - Damages/Expired</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Current Assets</t>
+          <t>Damages/Expiries</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>12020000</t>
+          <t>12010501</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>12000000</t>
+          <t>12010200</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Customer Control Accounts</t>
+          <t>Trade Receivables</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Trade Receivables</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>12020100</t>
+          <t>12020000</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>12020000</t>
+          <t>12000000</t>
         </is>
       </c>
       <c r="E75" t="n">
         <v>1</v>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Receivable</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Export Customers</t>
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Customer Control Accounts</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Customer Control Accounts</t>
+          <t>Trade Receivables</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>12020101</t>
+          <t>12020100</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>12020100</t>
+          <t>12020000</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2754,178 +2754,178 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>Export Customers</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Customer Control Accounts</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>12020101</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>12020100</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>Local Customers</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>Customer Control Accounts</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>12020102</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>12020100</t>
         </is>
       </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" t="inlineStr">
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>Receivable</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Unallocated Recievables</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Trade Receivables</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t>12020110</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>12020000</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Unallocated Recievables</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Unallocated Recievables</t>
+          <t>Trade Receivables</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>12020105</t>
+          <t>12020110</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>12020110</t>
+          <t>12020000</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Receivable</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>Cash &amp; Bank Equivalents</t>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unallocated Recievables</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Current Assets</t>
+          <t>Unallocated Recievables</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>12030000</t>
+          <t>12020105</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>12000000</t>
+          <t>12020110</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Receivable</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Bank Equivalents</t>
+          <t>Cash &amp; Bank Equivalents</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cash &amp; Bank Equivalents</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>12030100</t>
+          <t>12030000</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>12030000</t>
+          <t>12000000</t>
         </is>
       </c>
       <c r="E81" t="n">
         <v>1</v>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>ABSA Bank (UGX)</t>
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Bank Equivalents</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bank Equivalents</t>
+          <t>Cash &amp; Bank Equivalents</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>12030107</t>
+          <t>12030100</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>12030100</t>
+          <t>12030000</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -2936,69 +2936,69 @@
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>Cash Accounts</t>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ABSA Bank (UGX)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cash &amp; Bank Equivalents</t>
+          <t>Bank Equivalents</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>12030300</t>
+          <t>12030107</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>12030000</t>
+          <t>12030100</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
-      </c>
-      <c r="F83" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Airtel Money Pay</t>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Cash Accounts</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cash Accounts</t>
+          <t>Cash &amp; Bank Equivalents</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>12030301</t>
+          <t>12030300</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>12030300</t>
+          <t>12030000</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Momo Pay</t>
+          <t>Airtel Money Pay</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>12030303</t>
+          <t>12030301</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -3030,7 +3030,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Post Dated Cheques</t>
+          <t>Momo Pay</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>12030304</t>
+          <t>12030303</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -3051,65 +3051,65 @@
       <c r="E86" t="n">
         <v>0</v>
       </c>
-      <c r="F86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Cash - In -Hand</t>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Post Dated Cheques</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cash &amp; Bank Equivalents</t>
+          <t>Cash Accounts</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>12030400</t>
+          <t>12030304</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>12030000</t>
+          <t>12030300</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Petty Cash</t>
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Cash - In -Hand</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cash - In -Hand</t>
+          <t>Cash &amp; Bank Equivalents</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>12030401</t>
+          <t>12030400</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>12030400</t>
+          <t>12030000</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Donation-Clearing A/c</t>
+          <t>Petty Cash</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>12030402</t>
+          <t>12030401</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -3143,14 +3143,18 @@
       <c r="E89" t="n">
         <v>0</v>
       </c>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cash Lost A/C</t>
+          <t>Donation-Clearing A/c</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3160,7 +3164,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>12030403</t>
+          <t>12030402</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -3178,7 +3182,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CASH ACCOUNT</t>
+          <t>Cash Lost A/C</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3188,7 +3192,7 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>12030404</t>
+          <t>12030403</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -3199,18 +3203,14 @@
       <c r="E91" t="n">
         <v>0</v>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Bounced Cheque</t>
+          <t>CASH ACCOUNT</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>12030405</t>
+          <t>12030404</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -3231,33 +3231,37 @@
       <c r="E92" t="n">
         <v>0</v>
       </c>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>Other Receivables</t>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Bounced Cheque</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Current Assets</t>
+          <t>Cash - In -Hand</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>12040000</t>
+          <t>12030405</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>12000000</t>
+          <t>12030400</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
@@ -3266,22 +3270,22 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Related Party Receivables - Staff Advance</t>
+          <t>Other Receivables</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Other Receivables</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>12040100</t>
+          <t>12040000</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>12040000</t>
+          <t>12000000</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -3292,65 +3296,65 @@
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Staff Advances</t>
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Related Party Receivables - Staff Advance</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Related Party Receivables - Staff Advance</t>
+          <t>Other Receivables</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>12040102</t>
+          <t>12040100</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>12040100</t>
+          <t>12040000</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>Other Receivables</t>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Staff Advances</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Other Receivables</t>
+          <t>Related Party Receivables - Staff Advance</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>12040200</t>
+          <t>12040102</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>12040000</t>
+          <t>12040100</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Staff Loan</t>
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3360,16 +3364,16 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>12040201</t>
+          <t>12040200</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>12040200</t>
+          <t>12040000</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
@@ -3378,7 +3382,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Directors Loan Receivable</t>
+          <t>Staff Loan</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3388,7 +3392,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>12040202</t>
+          <t>12040201</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -3406,7 +3410,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Tax Receivable</t>
+          <t>Directors Loan Receivable</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3416,7 +3420,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>12040203</t>
+          <t>12040202</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -3434,17 +3438,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>Tax Receivable</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
           <t>Other Receivables</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Other Receivables</t>
-        </is>
-      </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>12040204</t>
+          <t>12040203</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
@@ -3462,7 +3466,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Withholding Tax Recivable</t>
+          <t>Other Receivables</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3472,7 +3476,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>12040205</t>
+          <t>12040204</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -3490,7 +3494,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Staff Advance</t>
+          <t>Withholding Tax Recivable</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3500,7 +3504,7 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>12040206</t>
+          <t>12040205</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -3516,9 +3520,9 @@
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Prepayments Expenses</t>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Staff Advance</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3528,44 +3532,44 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>12040300</t>
+          <t>12040206</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>12040000</t>
+          <t>12040200</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Prepaid Insurance</t>
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Prepayments Expenses</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Prepayments Expenses</t>
+          <t>Other Receivables</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>12040301</t>
+          <t>12040300</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>12040300</t>
+          <t>12040000</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
@@ -3574,7 +3578,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Supplier Advance</t>
+          <t>Prepaid Insurance</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3584,7 +3588,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>12040302</t>
+          <t>12040301</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -3602,7 +3606,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Prepaid Rent</t>
+          <t>Supplier Advance</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3612,7 +3616,7 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>12040303</t>
+          <t>12040302</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
@@ -3630,7 +3634,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Prepaid Tax</t>
+          <t>Prepaid Rent</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3640,7 +3644,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>12040304</t>
+          <t>12040303</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -3658,7 +3662,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Withholding Tax</t>
+          <t>Prepaid Tax</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3668,7 +3672,7 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>12040306</t>
+          <t>12040304</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
@@ -3686,7 +3690,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Other Prepayments</t>
+          <t>Withholding Tax</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3696,7 +3700,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>12040307</t>
+          <t>12040306</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
@@ -3712,56 +3716,56 @@
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Prepayment To Suppliers</t>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Other Prepayments</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Other Receivables</t>
+          <t>Prepayments Expenses</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>12040400</t>
+          <t>12040307</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>12040000</t>
+          <t>12040300</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Prepayment - International Suppliers</t>
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Prepayment To Suppliers</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Prepayment To Suppliers</t>
+          <t>Other Receivables</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>12040401</t>
+          <t>12040400</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>12040400</t>
+          <t>12040000</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
@@ -3770,7 +3774,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Prepayment - Local Suppliers</t>
+          <t>Prepayment - International Suppliers</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3780,7 +3784,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>12040402</t>
+          <t>12040401</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
@@ -3796,76 +3800,76 @@
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>Liabilities</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Prepayment - Local Suppliers</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Prepayment To Suppliers</t>
+        </is>
+      </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>20000000</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr"/>
+          <t>12040402</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>12040400</t>
+        </is>
+      </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Liability</t>
-        </is>
-      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Non Current Liabilities</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
           <t>Liabilities</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr"/>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>21000000</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
           <t>20000000</t>
         </is>
       </c>
+      <c r="D114" s="3" t="inlineStr"/>
       <c r="E114" t="n">
         <v>1</v>
       </c>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Liability</t>
+        </is>
+      </c>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Long Term Liability</t>
+          <t>Non Current Liabilities</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Non Current Liabilities</t>
+          <t>Liabilities</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>21010000</t>
+          <t>21000000</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>21000000</t>
+          <t>20000000</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -3878,22 +3882,22 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Mortgage Loan</t>
+          <t>Long Term Liability</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Long Term Liability</t>
+          <t>Non Current Liabilities</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>21010100</t>
+          <t>21010000</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>21010000</t>
+          <t>21000000</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -3904,168 +3908,168 @@
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Mortgage Loan Payable</t>
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Mortgage Loan</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Mortgage Loan</t>
+          <t>Long Term Liability</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>21010101</t>
+          <t>21010100</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>21010100</t>
+          <t>21010000</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>Bank Loan</t>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Mortgage Loan Payable</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Long Term Liability</t>
+          <t>Mortgage Loan</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>21010200</t>
+          <t>21010101</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>21010000</t>
+          <t>21010100</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Bank Loan Payable</t>
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Bank Loan</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Bank Loan</t>
+          <t>Long Term Liability</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>21010201</t>
+          <t>21010200</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>21010200</t>
+          <t>21010000</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>Related Party Borrowings</t>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Bank Loan Payable</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Long Term Liability</t>
+          <t>Bank Loan</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>21010300</t>
+          <t>21010201</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>21010000</t>
+          <t>21010200</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Directors Loan Payable</t>
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Related Party Borrowings</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Related Party Borrowings</t>
+          <t>Long Term Liability</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>21010301</t>
+          <t>21010300</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>21010300</t>
+          <t>21010000</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>Short Term Liability</t>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Directors Loan Payable</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Non Current Liabilities</t>
+          <t>Related Party Borrowings</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>21020000</t>
+          <t>21010301</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>21000000</t>
+          <t>21010300</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
@@ -4074,22 +4078,22 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Bank Loan Short Term Liabily</t>
+          <t>Short Term Liability</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Short Term Liability</t>
+          <t>Non Current Liabilities</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>21020100</t>
+          <t>21020000</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>21020000</t>
+          <t>21000000</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -4100,56 +4104,56 @@
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Short Term Loan Payable</t>
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Bank Loan Short Term Liabily</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Bank Loan Short Term Liabily</t>
+          <t>Short Term Liability</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>21020101</t>
+          <t>21020100</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>21020100</t>
+          <t>21020000</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>Current Liabilities</t>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Short Term Loan Payable</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Liabilities</t>
+          <t>Bank Loan Short Term Liabily</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>22000000</t>
+          <t>21020101</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>20000000</t>
+          <t>21020100</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
@@ -4158,22 +4162,22 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Trade Payables</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>Liabilities</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>22010000</t>
+          <t>22000000</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>22000000</t>
+          <t>20000000</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -4186,22 +4190,22 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Accounts Payables</t>
+          <t>Trade Payables</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Trade Payables</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>22010100</t>
+          <t>22010000</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>22010000</t>
+          <t>22000000</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -4212,41 +4216,37 @@
       <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Creditors Control - Local</t>
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Accounts Payables</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Accounts Payables</t>
+          <t>Trade Payables</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>22010101</t>
+          <t>22010100</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>22010100</t>
+          <t>22010000</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Payable</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Creditors Control - Foreign (GBP)</t>
+          <t>Creditors Control - Local</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>22010102</t>
+          <t>22010101</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -4267,18 +4267,18 @@
       <c r="E129" t="n">
         <v>0</v>
       </c>
-      <c r="F129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Payable</t>
+        </is>
+      </c>
       <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
+      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Reconciliation difference</t>
+          <t>Creditors Control - Foreign (GBP)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>22010103</t>
+          <t>22010102</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
@@ -4301,12 +4301,16 @@
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Credit Control Account Foreign (USD)</t>
+          <t>Reconciliation difference</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4316,7 +4320,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>22010104</t>
+          <t>22010103</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -4329,153 +4333,153 @@
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>Insurance Payable</t>
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Credit Control Account Foreign (USD)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Trade Payables</t>
+          <t>Accounts Payables</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>22010200</t>
+          <t>22010104</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>22010000</t>
+          <t>22010100</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Insurance- Gds In Transit/po.n.-9000/062/1/00217/2017</t>
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Payable</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Insurance Payable</t>
+          <t>Trade Payables</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>22010201</t>
+          <t>22010200</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>22010200</t>
+          <t>22010000</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>Stock Liability</t>
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Insurance- Gds In Transit/po.n.-9000/062/1/00217/2017</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Trade Payables</t>
+          <t>Insurance Payable</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>22010400</t>
+          <t>22010201</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>22010000</t>
+          <t>22010200</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Goods Received But Not Invoiced</t>
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Stock Liability</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Stock Liability</t>
+          <t>Trade Payables</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>22010401</t>
+          <t>22010400</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>22010400</t>
+          <t>22010000</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0</v>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Stock Received But Not Billed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>Other Payables</t>
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Goods Received But Not Invoiced</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>Stock Liability</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>22020000</t>
+          <t>22010401</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>22000000</t>
+          <t>22010400</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1</v>
-      </c>
-      <c r="F136" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Stock Received But Not Billed</t>
+        </is>
+      </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -4487,17 +4491,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Other Payables</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>22020100</t>
+          <t>22020000</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>22020000</t>
+          <t>22000000</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -4508,9 +4512,9 @@
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Interest Payable</t>
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Other Payables</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4520,16 +4524,16 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>22020101</t>
+          <t>22020100</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>22020100</t>
+          <t>22020000</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
@@ -4538,17 +4542,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>Interest Payable</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
           <t>Other Payables</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Other Payables</t>
-        </is>
-      </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>22020102</t>
+          <t>22020101</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -4566,7 +4570,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Savings Payable</t>
+          <t>Other Payables</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4576,7 +4580,7 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>22020103</t>
+          <t>22020102</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
@@ -4594,7 +4598,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Security Deposit Payable</t>
+          <t>Savings Payable</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4604,7 +4608,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>22020104</t>
+          <t>22020103</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -4622,7 +4626,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Employee Control</t>
+          <t>Security Deposit Payable</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4632,7 +4636,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>22020205</t>
+          <t>22020104</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
@@ -4648,9 +4652,9 @@
       <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>Interest Payable</t>
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Employee Control</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4660,72 +4664,72 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>22020200</t>
+          <t>22020205</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>22020000</t>
+          <t>22020100</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>Interest Payable</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Interest Payable</t>
+          <t>Other Payables</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>22020201</t>
+          <t>22020200</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>22020200</t>
+          <t>22020000</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>Landed Costs</t>
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Interest Payable</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>Interest Payable</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>22030000</t>
+          <t>22020201</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>22000000</t>
+          <t>22020200</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr"/>
@@ -4734,22 +4738,22 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>landed Cost Accounts</t>
+          <t>Landed Costs</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Landed Costs</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>22030100</t>
+          <t>22030000</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>22030000</t>
+          <t>22000000</t>
         </is>
       </c>
       <c r="E146" t="n">
@@ -4760,28 +4764,28 @@
       <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Agency Fee</t>
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>landed Cost Accounts</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>landed Cost Accounts</t>
+          <t>Landed Costs</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>22030101</t>
+          <t>22030100</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>22030100</t>
+          <t>22030000</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
@@ -4790,7 +4794,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Excise Duty</t>
+          <t>Agency Fee</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4800,7 +4804,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>22030103</t>
+          <t>22030101</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
@@ -4818,7 +4822,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Freight</t>
+          <t>Excise Duty</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4828,7 +4832,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>22030104</t>
+          <t>22030103</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -4841,16 +4845,12 @@
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
+      <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ICD Handling</t>
+          <t>Freight</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>22030105</t>
+          <t>22030104</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
@@ -4873,12 +4873,16 @@
       </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Import Duty</t>
+          <t>ICD Handling</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4888,7 +4892,7 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>22030106</t>
+          <t>22030105</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
@@ -4906,7 +4910,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Import Duty</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4916,7 +4920,7 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>22030107</t>
+          <t>22030106</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
@@ -4934,7 +4938,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4944,7 +4948,7 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>22030110</t>
+          <t>22030107</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -4962,7 +4966,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Clearance Uganda</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4972,7 +4976,7 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>22030112</t>
+          <t>22030110</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
@@ -4990,7 +4994,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Infrastructure Levy</t>
+          <t>Clearance Uganda</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5000,7 +5004,7 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>22030117</t>
+          <t>22030112</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
@@ -5018,7 +5022,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Freight GBP</t>
+          <t>Infrastructure Levy</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5028,7 +5032,7 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>22030124</t>
+          <t>22030117</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
@@ -5041,59 +5045,59 @@
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
+      <c r="H156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>Tax Payables</t>
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Freight GBP</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>landed Cost Accounts</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>22040000</t>
+          <t>22030124</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>22000000</t>
+          <t>22030100</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Tax Liabilities</t>
+          <t>Tax Payables</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Tax Payables</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>22040100</t>
+          <t>22040000</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>22040000</t>
+          <t>22000000</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -5104,28 +5108,28 @@
       <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Corporation Tax Payable</t>
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Tax Liabilities</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Tax Liabilities</t>
+          <t>Tax Payables</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>22040102</t>
+          <t>22040100</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>22040100</t>
+          <t>22040000</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr"/>
@@ -5134,7 +5138,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Withholding Tax Payable</t>
+          <t>Corporation Tax Payable</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5144,7 +5148,7 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>22040103</t>
+          <t>22040102</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
@@ -5155,18 +5159,14 @@
       <c r="E160" t="n">
         <v>0</v>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Tax</t>
-        </is>
-      </c>
+      <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Local Service Tax Payable</t>
+          <t>Withholding Tax Payable</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>22040104</t>
+          <t>22040103</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -5187,14 +5187,18 @@
       <c r="E161" t="n">
         <v>0</v>
       </c>
-      <c r="F161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Deffered Tax Payable</t>
+          <t>Local Service Tax Payable</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5204,7 +5208,7 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>22040105</t>
+          <t>22040104</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
@@ -5222,7 +5226,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Other Tax Payable</t>
+          <t>Deffered Tax Payable</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5232,7 +5236,7 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>22040106</t>
+          <t>22040105</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -5243,18 +5247,14 @@
       <c r="E163" t="n">
         <v>0</v>
       </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Tax</t>
-        </is>
-      </c>
+      <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Excise Duty Tax Payable</t>
+          <t>Other Tax Payable</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>22040107</t>
+          <t>22040106</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
@@ -5286,7 +5286,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Vat Payable</t>
+          <t>Excise Duty Tax Payable</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>22040101</t>
+          <t>22040107</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -5318,7 +5318,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Income Tax Payable</t>
+          <t>Vat Payable</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>22040108</t>
+          <t>22040101</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
@@ -5339,33 +5339,37 @@
       <c r="E166" t="n">
         <v>0</v>
       </c>
-      <c r="F166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>Payroll Liabilities</t>
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Income Tax Payable</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>Tax Liabilities</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>22050000</t>
+          <t>22040108</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>22000000</t>
+          <t>22040100</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
@@ -5379,17 +5383,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Payroll Liabilities</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>22050100</t>
+          <t>22050000</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>22050000</t>
+          <t>22000000</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -5400,9 +5404,9 @@
       <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Payroll Payable</t>
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Payroll Liabilities</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5412,16 +5416,16 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>22050101</t>
+          <t>22050100</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>22050100</t>
+          <t>22050000</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
@@ -5430,7 +5434,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Paye Payable</t>
+          <t>Payroll Payable</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5440,7 +5444,7 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>22050102</t>
+          <t>22050101</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -5458,7 +5462,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Nssf Payable</t>
+          <t>Paye Payable</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5468,7 +5472,7 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>22050103</t>
+          <t>22050102</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
@@ -5486,7 +5490,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Employee Saving Scheme</t>
+          <t>Nssf Payable</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5496,7 +5500,7 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>22050104</t>
+          <t>22050103</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -5514,7 +5518,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Employee Health Ins Payable</t>
+          <t>Employee Saving Scheme</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5524,7 +5528,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>22050105</t>
+          <t>22050104</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -5542,7 +5546,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Worker's Compensation</t>
+          <t>Employee Health Ins Payable</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5552,7 +5556,7 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>22050106</t>
+          <t>22050105</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
@@ -5570,7 +5574,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Staff Other Expenses Payable</t>
+          <t>Worker's Compensation</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5580,7 +5584,7 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>22050107</t>
+          <t>22050106</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -5598,7 +5602,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Staff Advances</t>
+          <t>Staff Other Expenses Payable</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5608,7 +5612,7 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>22050108</t>
+          <t>22050107</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
@@ -5624,28 +5628,28 @@
       <c r="H176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="inlineStr">
-        <is>
-          <t>Provisions &amp; Accruals</t>
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Staff Advances</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>Payroll Liabilities</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>22060000</t>
+          <t>22050108</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>22000000</t>
+          <t>22050100</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr"/>
@@ -5659,17 +5663,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Provisions &amp; Accruals</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>22060100</t>
+          <t>22060000</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>22060000</t>
+          <t>22000000</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -5680,9 +5684,9 @@
       <c r="H178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Warranties</t>
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Provisions &amp; Accruals</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5692,25 +5696,25 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>22060101</t>
+          <t>22060100</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>22060100</t>
+          <t>22060000</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>Deferred Income</t>
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Warranties</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5720,71 +5724,75 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>22060200</t>
+          <t>22060101</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>22060000</t>
+          <t>22060100</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Deferred Income (unearned Revenue)</t>
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Deferred Income</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Deferred Income</t>
+          <t>Provisions &amp; Accruals</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>22060201</t>
+          <t>22060200</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>22060200</t>
+          <t>22060000</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>Equity &amp; Reserve</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr"/>
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Deferred Income (unearned Revenue)</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Deferred Income</t>
+        </is>
+      </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>30000000</t>
-        </is>
-      </c>
-      <c r="D182" s="3" t="inlineStr"/>
+          <t>22060201</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>22060200</t>
+        </is>
+      </c>
       <c r="E182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
+      <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
     </row>
     <row r="183">
@@ -5793,32 +5801,28 @@
           <t>Equity &amp; Reserve</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Equity &amp; Reserve</t>
-        </is>
-      </c>
+      <c r="B183" t="inlineStr"/>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>31000000</t>
-        </is>
-      </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
           <t>30000000</t>
         </is>
       </c>
+      <c r="D183" s="3" t="inlineStr"/>
       <c r="E183" t="n">
         <v>1</v>
       </c>
       <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
       <c r="H183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Capital &amp; Reserves</t>
+          <t>Equity &amp; Reserve</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5828,12 +5832,12 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>31010000</t>
+          <t>31000000</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>31000000</t>
+          <t>30000000</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -5846,22 +5850,22 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Share Capital</t>
+          <t>Capital &amp; Reserves</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Capital &amp; Reserves</t>
+          <t>Equity &amp; Reserve</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>31010100</t>
+          <t>31010000</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>31010000</t>
+          <t>31000000</t>
         </is>
       </c>
       <c r="E185" t="n">
@@ -5872,28 +5876,28 @@
       <c r="H185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Ordinary Share Capital</t>
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Share Capital</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Share Capital</t>
+          <t>Capital &amp; Reserves</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>31010101</t>
+          <t>31010100</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>31010100</t>
+          <t>31010000</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
@@ -5902,7 +5906,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Preferred Shares</t>
+          <t>Ordinary Share Capital</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5912,7 +5916,7 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>31010102</t>
+          <t>31010101</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
@@ -5930,7 +5934,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Share Premium</t>
+          <t>Preferred Shares</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5940,7 +5944,7 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>31010103</t>
+          <t>31010102</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
@@ -5956,284 +5960,284 @@
       <c r="H188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="inlineStr">
-        <is>
-          <t>Dividends Paid</t>
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Share Premium</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Capital &amp; Reserves</t>
+          <t>Share Capital</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>31010200</t>
+          <t>31010103</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>31010000</t>
+          <t>31010100</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Shareholder Distributions</t>
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Dividends Paid</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Dividends Paid</t>
+          <t>Capital &amp; Reserves</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>31010104</t>
+          <t>31010200</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>31010200</t>
+          <t>31010000</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="inlineStr">
-        <is>
-          <t>Capital Grant</t>
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Shareholder Distributions</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Capital &amp; Reserves</t>
+          <t>Dividends Paid</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>31010300</t>
+          <t>31010104</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>31010000</t>
+          <t>31010200</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>Capital Grant</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Capital Grant</t>
+          <t>Capital &amp; Reserves</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>31010301</t>
+          <t>31010300</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>31010300</t>
+          <t>31010000</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>Directors Drawings</t>
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Capital Grant</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Capital &amp; Reserves</t>
+          <t>Capital Grant</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>31010400</t>
+          <t>31010301</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>31010000</t>
+          <t>31010300</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>Directors Drawings</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Directors Drawings</t>
+          <t>Capital &amp; Reserves</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>31010401</t>
+          <t>31010400</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>31010400</t>
+          <t>31010000</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>Retained Earnings</t>
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Directors Drawings</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Capital &amp; Reserves</t>
+          <t>Directors Drawings</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>31010500</t>
+          <t>31010401</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>31010000</t>
+          <t>31010400</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>Retained Earnings</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Retained Earnings</t>
+          <t>Capital &amp; Reserves</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>31010501</t>
+          <t>31010500</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>31010500</t>
+          <t>31010000</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>0</v>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="inlineStr">
-        <is>
-          <t>Other Reservces</t>
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Capital &amp; Reserves</t>
+          <t>Retained Earnings</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>31010600</t>
+          <t>31010501</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>31010000</t>
+          <t>31010500</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1</v>
-      </c>
-      <c r="F197" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Revaluation Reserve</t>
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Other Reservces</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Other Reservces</t>
+          <t>Capital &amp; Reserves</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>31010601</t>
+          <t>31010600</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>31010600</t>
+          <t>31010000</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr"/>
@@ -6242,7 +6246,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Capital Reserve</t>
+          <t>Revaluation Reserve</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6252,7 +6256,7 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>31010602</t>
+          <t>31010601</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
@@ -6270,7 +6274,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Exchange Difference Reserve</t>
+          <t>Capital Reserve</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6280,7 +6284,7 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>31010603</t>
+          <t>31010602</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
@@ -6296,27 +6300,31 @@
       <c r="H200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr"/>
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Exchange Difference Reserve</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Other Reservces</t>
+        </is>
+      </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>40000000</t>
-        </is>
-      </c>
-      <c r="D201" s="3" t="inlineStr"/>
+          <t>31010603</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>31010600</t>
+        </is>
+      </c>
       <c r="E201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>Income</t>
-        </is>
-      </c>
+      <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
     </row>
     <row r="202">
@@ -6325,32 +6333,28 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
+      <c r="B202" t="inlineStr"/>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>41000000</t>
-        </is>
-      </c>
-      <c r="D202" s="3" t="inlineStr">
-        <is>
           <t>40000000</t>
         </is>
       </c>
+      <c r="D202" s="3" t="inlineStr"/>
       <c r="E202" t="n">
         <v>1</v>
       </c>
       <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
       <c r="H202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>Stock Revenue</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6360,12 +6364,12 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>41010000</t>
+          <t>41000000</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>41000000</t>
+          <t>40000000</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -6383,17 +6387,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Stock Revenue</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>41010100</t>
+          <t>41010000</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>41010000</t>
+          <t>41000000</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -6406,7 +6410,7 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>Robusta Sales</t>
+          <t>Stock Revenue</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6416,12 +6420,12 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>41010110</t>
+          <t>41010100</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>41010100</t>
+          <t>41010000</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -6432,41 +6436,37 @@
       <c r="H205" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Robusta Screen 18 Sales</t>
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Robusta Sales</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Robusta Sales</t>
+          <t>Stock Revenue</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>41010111</t>
+          <t>41010110</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>41010110</t>
+          <t>41010100</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>0</v>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>Income Account</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Robusta Screen 15 Sales</t>
+          <t>Robusta Screen 18 Sales</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>41010112</t>
+          <t>41010111</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
@@ -6498,7 +6498,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Robusta Screen 12 Sales</t>
+          <t>Robusta Screen 15 Sales</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>41010113</t>
+          <t>41010112</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
@@ -6530,7 +6530,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Robusta Undergrade Sales</t>
+          <t>Robusta Screen 12 Sales</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>41010114</t>
+          <t>41010113</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
@@ -6560,69 +6560,69 @@
       <c r="H209" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>Arabica Sales</t>
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Robusta Undergrade Sales</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Stock Revenue</t>
+          <t>Robusta Sales</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>41010120</t>
+          <t>41010114</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>41010100</t>
+          <t>41010110</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1</v>
-      </c>
-      <c r="F210" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Income Account</t>
+        </is>
+      </c>
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Arabica Screen 18 Sales</t>
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Arabica Sales</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Arabica Sales</t>
+          <t>Stock Revenue</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>41010121</t>
+          <t>41010120</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>41010120</t>
+          <t>41010100</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>0</v>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>Income Account</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Arabica Screen 15 Sales</t>
+          <t>Arabica Screen 18 Sales</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>41010122</t>
+          <t>41010121</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
@@ -6654,7 +6654,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Arabica Screen 12 Sales</t>
+          <t>Arabica Screen 15 Sales</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>41010123</t>
+          <t>41010122</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
@@ -6686,7 +6686,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Arabica Undergrade Sales</t>
+          <t>Arabica Screen 12 Sales</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>41010124</t>
+          <t>41010123</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
@@ -6718,22 +6718,22 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>By-product Sales</t>
+          <t>Arabica Undergrade Sales</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Stock Revenue</t>
+          <t>Arabica Sales</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>41010130</t>
+          <t>41010124</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>41010100</t>
+          <t>41010120</t>
         </is>
       </c>
       <c r="E215" t="n">
@@ -6748,30 +6748,34 @@
       <c r="H215" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>Other Income</t>
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>By-product Sales</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Stock Revenue</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>41020000</t>
+          <t>41010130</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>41000000</t>
+          <t>41010100</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1</v>
-      </c>
-      <c r="F216" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Income Account</t>
+        </is>
+      </c>
       <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr"/>
     </row>
@@ -6783,17 +6787,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>41020100</t>
+          <t>41020000</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>41020000</t>
+          <t>41000000</t>
         </is>
       </c>
       <c r="E217" t="n">
@@ -6804,9 +6808,9 @@
       <c r="H217" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Interest Income</t>
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6816,16 +6820,16 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>41020101</t>
+          <t>41020100</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>41020100</t>
+          <t>41020000</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr"/>
@@ -6834,7 +6838,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Inventory Income</t>
+          <t>Interest Income</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6844,7 +6848,7 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>41020102</t>
+          <t>41020101</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
@@ -6862,7 +6866,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Rounding Gain</t>
+          <t>Inventory Income</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6872,7 +6876,7 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>41020103</t>
+          <t>41020102</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
@@ -6890,7 +6894,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Exchange Gain</t>
+          <t>Rounding Gain</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6900,7 +6904,7 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>41020104</t>
+          <t>41020103</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
@@ -6918,7 +6922,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Asset Disposal Gain</t>
+          <t>Exchange Gain</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6928,7 +6932,7 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>41020105</t>
+          <t>41020104</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
@@ -6946,17 +6950,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
+          <t>Asset Disposal Gain</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
           <t>Other Income</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Other Income</t>
-        </is>
-      </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>41020106</t>
+          <t>41020105</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -6974,7 +6978,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Other Discount Income</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6984,7 +6988,7 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>41020107</t>
+          <t>41020106</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
@@ -7000,76 +7004,76 @@
       <c r="H224" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>Cost of Goods</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr"/>
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Other Discount Income</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>50000000</t>
-        </is>
-      </c>
-      <c r="D225" s="3" t="inlineStr"/>
+          <t>41020107</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>41020100</t>
+        </is>
+      </c>
       <c r="E225" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
+      <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Cost Of Goods Sold</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
           <t>Cost of Goods</t>
         </is>
       </c>
+      <c r="B226" t="inlineStr"/>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>51000000</t>
-        </is>
-      </c>
-      <c r="D226" s="3" t="inlineStr">
-        <is>
           <t>50000000</t>
         </is>
       </c>
+      <c r="D226" s="3" t="inlineStr"/>
       <c r="E226" t="n">
         <v>1</v>
       </c>
       <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
       <c r="H226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>Direct Cost Of Goods Sold</t>
+          <t>Cost Of Goods Sold</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Cost Of Goods Sold</t>
+          <t>Cost of Goods</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>51010000</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>51000000</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -7082,22 +7086,22 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Cost Of Sales</t>
+          <t>Direct Cost Of Goods Sold</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Direct Cost Of Goods Sold</t>
+          <t>Cost Of Goods Sold</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>51010100</t>
+          <t>51010000</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>51010000</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="E228" t="n">
@@ -7110,22 +7114,22 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>Robusta Cost of Sales</t>
+          <t>Cost Of Sales</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Cost Of Sales</t>
+          <t>Direct Cost Of Goods Sold</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>51010110</t>
+          <t>51010100</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>51010100</t>
+          <t>51010000</t>
         </is>
       </c>
       <c r="E229" t="n">
@@ -7136,41 +7140,37 @@
       <c r="H229" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>Robusta Screen 18 Cost of Sales</t>
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Robusta Cost of Sales</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Robusta Cost of Sales</t>
+          <t>Cost Of Sales</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>51010111</t>
+          <t>51010110</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>51010110</t>
+          <t>51010100</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>0</v>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>Cost of Goods Sold</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Robusta Screen 15 Cost of Sales</t>
+          <t>Robusta Screen 18 Cost of Sales</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>51010112</t>
+          <t>51010111</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
@@ -7202,7 +7202,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Robusta Screen 12 Cost of Sales</t>
+          <t>Robusta Screen 15 Cost of Sales</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>51010113</t>
+          <t>51010112</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
@@ -7234,7 +7234,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Robusta Undergrade Cost of Sales</t>
+          <t>Robusta Screen 12 Cost of Sales</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>51010114</t>
+          <t>51010113</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
@@ -7264,69 +7264,69 @@
       <c r="H233" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="inlineStr">
-        <is>
-          <t>Arabica Cost of Sales</t>
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Robusta Undergrade Cost of Sales</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Cost Of Sales</t>
+          <t>Robusta Cost of Sales</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>51010120</t>
+          <t>51010114</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>51010100</t>
+          <t>51010110</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>1</v>
-      </c>
-      <c r="F234" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Cost of Goods Sold</t>
+        </is>
+      </c>
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>Arabica Screen 18 Cost of Sales</t>
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Arabica Cost of Sales</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Arabica Cost of Sales</t>
+          <t>Cost Of Sales</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>51010121</t>
+          <t>51010120</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
-          <t>51010120</t>
+          <t>51010100</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>0</v>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>Cost of Goods Sold</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Arabica Screen 15 Cost of Sales</t>
+          <t>Arabica Screen 18 Cost of Sales</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>51010122</t>
+          <t>51010121</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
@@ -7358,7 +7358,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Arabica Screen 12 Cost of Sales</t>
+          <t>Arabica Screen 15 Cost of Sales</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>51010123</t>
+          <t>51010122</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
@@ -7390,7 +7390,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Arabica Undergrade Cost of Sales</t>
+          <t>Arabica Screen 12 Cost of Sales</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>51010124</t>
+          <t>51010123</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
@@ -7422,22 +7422,22 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>By-product Cost of Sales</t>
+          <t>Arabica Undergrade Cost of Sales</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Cost Of Sales</t>
+          <t>Arabica Cost of Sales</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>51010130</t>
+          <t>51010124</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>51010100</t>
+          <t>51010120</t>
         </is>
       </c>
       <c r="E239" t="n">
@@ -7452,52 +7452,56 @@
       <c r="H239" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>Indirect Cost Of Goods Sold</t>
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>By-product Cost of Sales</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Cost Of Goods Sold</t>
+          <t>Cost Of Sales</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>51020000</t>
+          <t>51010130</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>51000000</t>
+          <t>51010100</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>1</v>
-      </c>
-      <c r="F240" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Cost of Goods Sold</t>
+        </is>
+      </c>
       <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>Lost In Transit</t>
+          <t>Indirect Cost Of Goods Sold</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Indirect Cost Of Goods Sold</t>
+          <t>Cost Of Goods Sold</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>51010300</t>
+          <t>51020000</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
         <is>
-          <t>51020000</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="E241" t="n">
@@ -7508,97 +7512,93 @@
       <c r="H241" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
+      <c r="A242" s="2" t="inlineStr">
         <is>
           <t>Lost In Transit</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Lost In Transit</t>
+          <t>Indirect Cost Of Goods Sold</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>51010301</t>
+          <t>51010300</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>51010300</t>
+          <t>51020000</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="inlineStr">
-        <is>
-          <t>Stock Adjustments</t>
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Lost In Transit</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Indirect Cost Of Goods Sold</t>
+          <t>Lost In Transit</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>51020200</t>
+          <t>51010301</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>51020000</t>
+          <t>51010300</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>Stock Adjustment Account</t>
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Stock Adjustments</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Stock Adjustments</t>
+          <t>Indirect Cost Of Goods Sold</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>51010201</t>
+          <t>51020200</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>51020200</t>
+          <t>51020000</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>0</v>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>Stock Adjustment</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Stock Differences Account</t>
+          <t>Stock Adjustment Account</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>51010202</t>
+          <t>51010201</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -7619,14 +7619,18 @@
       <c r="E245" t="n">
         <v>0</v>
       </c>
-      <c r="F245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Stock Adjustment</t>
+        </is>
+      </c>
       <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Price Differences Account</t>
+          <t>Stock Differences Account</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7636,7 +7640,7 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>51010203</t>
+          <t>51010202</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
@@ -7654,7 +7658,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Expiry</t>
+          <t>Price Differences Account</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7664,7 +7668,7 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>51010205</t>
+          <t>51010203</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
@@ -7682,7 +7686,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Damanged Goods</t>
+          <t>Expiry</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7692,7 +7696,7 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>51010206</t>
+          <t>51010205</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
@@ -7708,28 +7712,28 @@
       <c r="H248" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="inlineStr">
-        <is>
-          <t>Discount Allowed</t>
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Damanged Goods</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Cost Of Goods Sold</t>
+          <t>Stock Adjustments</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>52010000</t>
+          <t>51010206</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>51000000</t>
+          <t>51020200</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr"/>
@@ -7743,17 +7747,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Discount Allowed</t>
+          <t>Cost Of Goods Sold</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>52010100</t>
+          <t>52010000</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>52010000</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="E250" t="n">
@@ -7764,7 +7768,7 @@
       <c r="H250" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
+      <c r="A251" s="2" t="inlineStr">
         <is>
           <t>Discount Allowed</t>
         </is>
@@ -7776,43 +7780,47 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>52010101</t>
+          <t>52010100</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
-          <t>52010100</t>
+          <t>52010000</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="inlineStr">
-        <is>
-          <t>Operating Cost</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr"/>
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Discount Allowed</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Discount Allowed</t>
+        </is>
+      </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>60000000</t>
-        </is>
-      </c>
-      <c r="D252" s="3" t="inlineStr"/>
+          <t>52010101</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>52010100</t>
+        </is>
+      </c>
       <c r="E252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
+      <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
     </row>
     <row r="253">
@@ -7821,26 +7829,22 @@
           <t>Operating Cost</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Operating Cost</t>
-        </is>
-      </c>
+      <c r="B253" t="inlineStr"/>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>61000000</t>
-        </is>
-      </c>
-      <c r="D253" s="3" t="inlineStr">
-        <is>
           <t>60000000</t>
         </is>
       </c>
+      <c r="D253" s="3" t="inlineStr"/>
       <c r="E253" t="n">
         <v>1</v>
       </c>
       <c r="F253" t="inlineStr"/>
-      <c r="G253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
       <c r="H253" t="inlineStr"/>
     </row>
     <row r="254">
@@ -7856,12 +7860,12 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>61010000</t>
+          <t>61000000</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>61000000</t>
+          <t>60000000</t>
         </is>
       </c>
       <c r="E254" t="n">
@@ -7884,12 +7888,12 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>61010100</t>
+          <t>61010000</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>61010000</t>
+          <t>61000000</t>
         </is>
       </c>
       <c r="E255" t="n">
@@ -7900,9 +7904,9 @@
       <c r="H255" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>Bank&amp;Finance Costs</t>
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -7912,16 +7916,16 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>61010101</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>61010100</t>
+          <t>61010000</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr"/>
@@ -7930,7 +7934,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Administrative Expenses</t>
+          <t>Bank&amp;Finance Costs</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -7940,7 +7944,7 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>61010102</t>
+          <t>61010101</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
@@ -7958,7 +7962,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Bad Debts</t>
+          <t>Administrative Expenses</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -7968,7 +7972,7 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>61010103</t>
+          <t>61010102</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
@@ -7986,7 +7990,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Commission - Coffee Agents</t>
+          <t>Bad Debts</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -7996,7 +8000,7 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>61010105</t>
+          <t>61010103</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
@@ -8014,7 +8018,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Commission on Delivery</t>
+          <t>Commission - Coffee Agents</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -8024,7 +8028,7 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>61010106</t>
+          <t>61010105</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
@@ -8042,7 +8046,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>DAMAGES AND EXPIRES</t>
+          <t>Commission on Delivery</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -8052,7 +8056,7 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>61010107</t>
+          <t>61010106</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
@@ -8070,7 +8074,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Damages&amp;Loss</t>
+          <t>DAMAGES AND EXPIRES</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -8080,7 +8084,7 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>61010108</t>
+          <t>61010107</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -8098,7 +8102,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Delivery Cost to Customers</t>
+          <t>Damages&amp;Loss</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -8108,7 +8112,7 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>61010109</t>
+          <t>61010108</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
@@ -8126,7 +8130,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Director's Allowances</t>
+          <t>Delivery Cost to Customers</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -8136,7 +8140,7 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>61010110</t>
+          <t>61010109</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
@@ -8154,7 +8158,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>DONATIONS</t>
+          <t>Director's Allowances</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -8164,7 +8168,7 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>61010111</t>
+          <t>61010110</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
@@ -8182,7 +8186,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Electricity Bills</t>
+          <t>DONATIONS</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -8192,7 +8196,7 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>61010112</t>
+          <t>61010111</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
@@ -8210,7 +8214,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Handling&amp;Agency Fees</t>
+          <t>Electricity Bills</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -8220,7 +8224,7 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>61010113</t>
+          <t>61010112</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
@@ -8238,7 +8242,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Income Tax</t>
+          <t>Handling&amp;Agency Fees</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -8248,7 +8252,7 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>61010114</t>
+          <t>61010113</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
@@ -8266,7 +8270,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Income Tax</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -8276,7 +8280,7 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>61010115</t>
+          <t>61010114</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
@@ -8294,7 +8298,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Legal Fees</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -8304,7 +8308,7 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>61010116</t>
+          <t>61010115</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
@@ -8322,7 +8326,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Licences&amp; Permits</t>
+          <t>Legal Fees</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -8332,7 +8336,7 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>61010117</t>
+          <t>61010116</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
@@ -8350,7 +8354,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>LOSSES</t>
+          <t>Licences&amp; Permits</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -8360,7 +8364,7 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>61010118</t>
+          <t>61010117</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
@@ -8378,7 +8382,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Marketing Expenses</t>
+          <t>LOSSES</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -8388,7 +8392,7 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>61010119</t>
+          <t>61010118</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
@@ -8406,7 +8410,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Miscellenous Exp</t>
+          <t>Marketing Expenses</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -8416,7 +8420,7 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>61010120</t>
+          <t>61010119</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
@@ -8434,7 +8438,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Motorbike Fuel &amp;Maintenance</t>
+          <t>Miscellenous Exp</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -8444,7 +8448,7 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>61010121</t>
+          <t>61010120</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
@@ -8462,7 +8466,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>NSSF Expenses</t>
+          <t>Motorbike Fuel &amp;Maintenance</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -8472,7 +8476,7 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>61010122</t>
+          <t>61010121</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
@@ -8490,7 +8494,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Office Expenses</t>
+          <t>NSSF Expenses</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -8500,7 +8504,7 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>61010123</t>
+          <t>61010122</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
@@ -8518,7 +8522,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Office Repairs &amp;Maintenance</t>
+          <t>Office Expenses</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -8528,7 +8532,7 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>61010124</t>
+          <t>61010123</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
@@ -8546,7 +8550,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Office Transport</t>
+          <t>Office Repairs &amp;Maintenance</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -8556,7 +8560,7 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>61010125</t>
+          <t>61010124</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
@@ -8574,7 +8578,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>Office Transport</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -8584,7 +8588,7 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>61010126</t>
+          <t>61010125</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
@@ -8602,7 +8606,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>PAYE</t>
+          <t>Packaging</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -8612,7 +8616,7 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>61010127</t>
+          <t>61010126</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
@@ -8630,7 +8634,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Rent Exp.</t>
+          <t>PAYE</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8640,7 +8644,7 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>61010128</t>
+          <t>61010127</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
@@ -8658,7 +8662,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Salaries &amp; Wages</t>
+          <t>Rent Exp.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8668,7 +8672,7 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>61010129</t>
+          <t>61010128</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
@@ -8686,7 +8690,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Security Expenses</t>
+          <t>Salaries &amp; Wages</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8696,7 +8700,7 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>61010130</t>
+          <t>61010129</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
@@ -8714,7 +8718,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Staff Allowance-Lunch</t>
+          <t>Security Expenses</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8724,7 +8728,7 @@
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>61010131</t>
+          <t>61010130</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
@@ -8742,7 +8746,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Staff Allowances-Transport</t>
+          <t>Staff Allowance-Lunch</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8752,7 +8756,7 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>61010132</t>
+          <t>61010131</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
@@ -8770,7 +8774,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Staff Bonus</t>
+          <t>Staff Allowances-Transport</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8780,7 +8784,7 @@
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>61010133</t>
+          <t>61010132</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
@@ -8798,7 +8802,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Staff Medical Expenses</t>
+          <t>Staff Bonus</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8808,7 +8812,7 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>61010134</t>
+          <t>61010133</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
@@ -8826,7 +8830,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Staff Uniforms</t>
+          <t>Staff Medical Expenses</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -8836,7 +8840,7 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>61010135</t>
+          <t>61010134</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
@@ -8854,7 +8858,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Staff Welfare</t>
+          <t>Staff Uniforms</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -8864,7 +8868,7 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>61010136</t>
+          <t>61010135</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
@@ -8882,7 +8886,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Stationery Expenses</t>
+          <t>Staff Welfare</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -8892,7 +8896,7 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>61010137</t>
+          <t>61010136</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
@@ -8910,7 +8914,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Telephone&amp;Internet Exp</t>
+          <t>Stationery Expenses</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -8920,7 +8924,7 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>61010138</t>
+          <t>61010137</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
@@ -8938,7 +8942,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Trading Licence &amp;Permits</t>
+          <t>Telephone&amp;Internet Exp</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -8948,7 +8952,7 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>61010139</t>
+          <t>61010138</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
@@ -8966,7 +8970,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Travelling Expenses</t>
+          <t>Trading Licence &amp;Permits</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -8976,7 +8980,7 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>61010140</t>
+          <t>61010139</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
@@ -8994,7 +8998,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Water Bills</t>
+          <t>Travelling Expenses</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -9004,7 +9008,7 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>61010141</t>
+          <t>61010140</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
@@ -9022,7 +9026,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Web Hosting</t>
+          <t>Water Bills</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -9032,7 +9036,7 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>61010142</t>
+          <t>61010141</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
@@ -9048,9 +9052,9 @@
       <c r="H296" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="inlineStr">
-        <is>
-          <t>Finance Cost</t>
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Web Hosting</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -9060,44 +9064,44 @@
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>63010200</t>
+          <t>61010142</t>
         </is>
       </c>
       <c r="D297" s="3" t="inlineStr">
         <is>
-          <t>61010000</t>
+          <t>61010100</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F297" t="inlineStr"/>
       <c r="G297" t="inlineStr"/>
       <c r="H297" t="inlineStr"/>
     </row>
     <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>Bank Charges</t>
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>Finance Cost</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Finance Cost</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>63010101</t>
+          <t>63010200</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>63010200</t>
+          <t>61010000</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="inlineStr"/>
@@ -9106,7 +9110,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Momo/Easy Pay Charges</t>
+          <t>Bank Charges</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -9116,7 +9120,7 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>63010102</t>
+          <t>63010101</t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr">
@@ -9134,7 +9138,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Interest Expense</t>
+          <t>Momo/Easy Pay Charges</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -9144,7 +9148,7 @@
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>63010103</t>
+          <t>63010102</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
@@ -9162,7 +9166,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Exchange Loss</t>
+          <t>Interest Expense</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -9172,7 +9176,7 @@
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>63010104</t>
+          <t>63010103</t>
         </is>
       </c>
       <c r="D301" s="3" t="inlineStr">
@@ -9190,7 +9194,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Unrealized Loss On Exchange Rate Differences</t>
+          <t>Exchange Loss</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -9200,7 +9204,7 @@
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>63010105</t>
+          <t>63010104</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
@@ -9218,7 +9222,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Rounding Loss</t>
+          <t>Unrealized Loss On Exchange Rate Differences</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -9228,7 +9232,7 @@
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>63010106</t>
+          <t>63010105</t>
         </is>
       </c>
       <c r="D303" s="3" t="inlineStr">
@@ -9239,18 +9243,14 @@
       <c r="E303" t="n">
         <v>0</v>
       </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>Round Off</t>
-        </is>
-      </c>
+      <c r="F303" t="inlineStr"/>
       <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Service Charge</t>
+          <t>Rounding Loss</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>63010107</t>
+          <t>63010106</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
@@ -9271,14 +9271,18 @@
       <c r="E304" t="n">
         <v>0</v>
       </c>
-      <c r="F304" t="inlineStr"/>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Round Off</t>
+        </is>
+      </c>
       <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Od Interest/service Change</t>
+          <t>Service Charge</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -9288,7 +9292,7 @@
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>63010108</t>
+          <t>63010107</t>
         </is>
       </c>
       <c r="D305" s="3" t="inlineStr">
@@ -9306,7 +9310,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Fake Notes</t>
+          <t>Od Interest/service Change</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -9316,7 +9320,7 @@
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>63010109</t>
+          <t>63010108</t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr">
@@ -9334,7 +9338,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Loan Processing fees</t>
+          <t>Fake Notes</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -9344,7 +9348,7 @@
       </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>63010110</t>
+          <t>63010109</t>
         </is>
       </c>
       <c r="D307" s="3" t="inlineStr">
@@ -9360,69 +9364,65 @@
       <c r="H307" t="inlineStr"/>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="inlineStr">
-        <is>
-          <t>Depreciation Expense</t>
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Loan Processing fees</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Finance Cost</t>
         </is>
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t>63010300</t>
+          <t>63010110</t>
         </is>
       </c>
       <c r="D308" s="3" t="inlineStr">
         <is>
-          <t>61010000</t>
+          <t>63010200</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F308" t="inlineStr"/>
       <c r="G308" t="inlineStr"/>
       <c r="H308" t="inlineStr"/>
     </row>
     <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>Depreciation Expense - Buildings</t>
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>Depreciation Expense</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Depreciation Expense</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C309" s="3" t="inlineStr">
         <is>
-          <t>63010301</t>
+          <t>63010300</t>
         </is>
       </c>
       <c r="D309" s="3" t="inlineStr">
         <is>
-          <t>63010300</t>
+          <t>61010000</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>0</v>
-      </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F309" t="inlineStr"/>
       <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Depreciation Expense -Furniture &amp; Fittings</t>
+          <t>Depreciation Expense - Buildings</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>63010302</t>
+          <t>63010301</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
@@ -9454,7 +9454,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Depreciation Expense - Machinery &amp; Equipment</t>
+          <t>Depreciation Expense -Furniture &amp; Fittings</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>63010303</t>
+          <t>63010302</t>
         </is>
       </c>
       <c r="D311" s="3" t="inlineStr">
@@ -9486,7 +9486,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Depreciation Expense - Motor Vehicles</t>
+          <t>Depreciation Expense - Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t>63010304</t>
+          <t>63010303</t>
         </is>
       </c>
       <c r="D312" s="3" t="inlineStr">
@@ -9518,7 +9518,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Computers &amp; Data Processing Equip</t>
+          <t>Depreciation Expense - Motor Vehicles</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="C313" s="3" t="inlineStr">
         <is>
-          <t>63010305</t>
+          <t>63010304</t>
         </is>
       </c>
       <c r="D313" s="3" t="inlineStr">
@@ -9548,56 +9548,60 @@
       <c r="H313" t="inlineStr"/>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="inlineStr">
-        <is>
-          <t>Other Expenses</t>
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Computers &amp; Data Processing Equip</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Depreciation Expense</t>
         </is>
       </c>
       <c r="C314" s="3" t="inlineStr">
         <is>
-          <t>63010500</t>
+          <t>63010305</t>
         </is>
       </c>
       <c r="D314" s="3" t="inlineStr">
         <is>
-          <t>61010000</t>
+          <t>63010300</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>1</v>
-      </c>
-      <c r="F314" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="G314" t="inlineStr"/>
       <c r="H314" t="inlineStr"/>
     </row>
     <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>Penalties &amp; Fines</t>
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C315" s="3" t="inlineStr">
         <is>
-          <t>63010501</t>
+          <t>63010500</t>
         </is>
       </c>
       <c r="D315" s="3" t="inlineStr">
         <is>
-          <t>63010500</t>
+          <t>61010000</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr"/>
@@ -9606,7 +9610,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Legal Expenses</t>
+          <t>Penalties &amp; Fines</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -9616,7 +9620,7 @@
       </c>
       <c r="C316" s="3" t="inlineStr">
         <is>
-          <t>63010502</t>
+          <t>63010501</t>
         </is>
       </c>
       <c r="D316" s="3" t="inlineStr">
@@ -9634,7 +9638,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Customs Penalty Tax</t>
+          <t>Legal Expenses</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -9644,7 +9648,7 @@
       </c>
       <c r="C317" s="3" t="inlineStr">
         <is>
-          <t>63010503</t>
+          <t>63010502</t>
         </is>
       </c>
       <c r="D317" s="3" t="inlineStr">
@@ -9662,7 +9666,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>Customs Penalty Tax</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -9672,7 +9676,7 @@
       </c>
       <c r="C318" s="3" t="inlineStr">
         <is>
-          <t>63010504</t>
+          <t>63010503</t>
         </is>
       </c>
       <c r="D318" s="3" t="inlineStr">
@@ -9690,7 +9694,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Realized Loss On Exchange Rate Differences</t>
+          <t>Donations</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -9700,7 +9704,7 @@
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>63010505</t>
+          <t>63010504</t>
         </is>
       </c>
       <c r="D319" s="3" t="inlineStr">
@@ -9718,7 +9722,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Unrealized Loss On Exchange Rate Differences</t>
+          <t>Realized Loss On Exchange Rate Differences</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -9728,7 +9732,7 @@
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>63010506</t>
+          <t>63010505</t>
         </is>
       </c>
       <c r="D320" s="3" t="inlineStr">
@@ -9746,7 +9750,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Loss / Gain On Asset Disposal</t>
+          <t>Unrealized Loss On Exchange Rate Differences</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -9756,7 +9760,7 @@
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>63010507</t>
+          <t>63010506</t>
         </is>
       </c>
       <c r="D321" s="3" t="inlineStr">
@@ -9774,7 +9778,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Tax Penalties</t>
+          <t>Loss / Gain On Asset Disposal</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -9784,7 +9788,7 @@
       </c>
       <c r="C322" s="3" t="inlineStr">
         <is>
-          <t>63010508</t>
+          <t>63010507</t>
         </is>
       </c>
       <c r="D322" s="3" t="inlineStr">
@@ -9800,69 +9804,65 @@
       <c r="H322" t="inlineStr"/>
     </row>
     <row r="323">
-      <c r="A323" s="2" t="inlineStr">
-        <is>
-          <t>Amortization Expense</t>
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Tax Penalties</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Other Expenses</t>
         </is>
       </c>
       <c r="C323" s="3" t="inlineStr">
         <is>
-          <t>63020400</t>
+          <t>63010508</t>
         </is>
       </c>
       <c r="D323" s="3" t="inlineStr">
         <is>
-          <t>61010000</t>
+          <t>63010500</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F323" t="inlineStr"/>
       <c r="G323" t="inlineStr"/>
       <c r="H323" t="inlineStr"/>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>Amortization Expense - Software &amp; Licenses</t>
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>Amortization Expense</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Amortization Expense</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C324" s="3" t="inlineStr">
         <is>
-          <t>63020401</t>
+          <t>63020400</t>
         </is>
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>63020400</t>
+          <t>61010000</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>0</v>
-      </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Amortization Expense - Goodwill</t>
+          <t>Amortization Expense - Software &amp; Licenses</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="C325" s="3" t="inlineStr">
         <is>
-          <t>63020402</t>
+          <t>63020401</t>
         </is>
       </c>
       <c r="D325" s="3" t="inlineStr">
@@ -9892,27 +9892,35 @@
       <c r="H325" t="inlineStr"/>
     </row>
     <row r="326">
-      <c r="A326" s="2" t="inlineStr">
-        <is>
-          <t>Opening Balance</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr"/>
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Amortization Expense - Goodwill</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Amortization Expense</t>
+        </is>
+      </c>
       <c r="C326" s="3" t="inlineStr">
         <is>
-          <t>90000000</t>
-        </is>
-      </c>
-      <c r="D326" s="3" t="inlineStr"/>
+          <t>63020402</t>
+        </is>
+      </c>
+      <c r="D326" s="3" t="inlineStr">
+        <is>
+          <t>63020400</t>
+        </is>
+      </c>
       <c r="E326" t="n">
-        <v>1</v>
-      </c>
-      <c r="F326" t="inlineStr"/>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>Liability</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr"/>
       <c r="H326" t="inlineStr"/>
     </row>
     <row r="327">
@@ -9921,26 +9929,22 @@
           <t>Opening Balance</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>Opening Balance</t>
-        </is>
-      </c>
+      <c r="B327" t="inlineStr"/>
       <c r="C327" s="3" t="inlineStr">
         <is>
-          <t>90100000</t>
-        </is>
-      </c>
-      <c r="D327" s="3" t="inlineStr">
-        <is>
           <t>90000000</t>
         </is>
       </c>
+      <c r="D327" s="3" t="inlineStr"/>
       <c r="E327" t="n">
         <v>1</v>
       </c>
       <c r="F327" t="inlineStr"/>
-      <c r="G327" t="inlineStr"/>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Liability</t>
+        </is>
+      </c>
       <c r="H327" t="inlineStr"/>
     </row>
     <row r="328">
@@ -9956,12 +9960,12 @@
       </c>
       <c r="C328" s="3" t="inlineStr">
         <is>
-          <t>90101000</t>
+          <t>90100000</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>90100000</t>
+          <t>90000000</t>
         </is>
       </c>
       <c r="E328" t="n">
@@ -9972,7 +9976,7 @@
       <c r="H328" t="inlineStr"/>
     </row>
     <row r="329">
-      <c r="A329" t="inlineStr">
+      <c r="A329" s="2" t="inlineStr">
         <is>
           <t>Opening Balance</t>
         </is>
@@ -9984,24 +9988,52 @@
       </c>
       <c r="C329" s="3" t="inlineStr">
         <is>
-          <t>901010100</t>
+          <t>90101000</t>
         </is>
       </c>
       <c r="D329" s="3" t="inlineStr">
         <is>
-          <t>90101000</t>
+          <t>90100000</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>0</v>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>Temporary</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F329" t="inlineStr"/>
       <c r="G329" t="inlineStr"/>
       <c r="H329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Opening Balance</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Opening Balance</t>
+        </is>
+      </c>
+      <c r="C330" s="3" t="inlineStr">
+        <is>
+          <t>901010100</t>
+        </is>
+      </c>
+      <c r="D330" s="3" t="inlineStr">
+        <is>
+          <t>90101000</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>0</v>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Temporary</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr"/>
+      <c r="H330" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
